--- a/VerveStacks_IND_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IND_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4B99D02-157C-424F-8EEA-8B903A9C18A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07A88271-ED4B-4CA5-8905-7EC01C5231A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="424">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -307,13 +307,301 @@
     <t>IND</t>
   </si>
   <si>
+    <t>w1246177377-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w1246177377-765_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt,en_gas_turbine,en_gas_chp,en_gas_fuelcell,en_gas_ccs,en_coal_subcritical,en_coal_supercritical,en_coal_ultrasupercritical,en_coal_igcc,en_coal_ccs,en_coal_igcc_ccs,en_coal_oxyfuel_ccs,en_nuclear,en_nuclear_smr,en_biomass,en_biomass_cofiring,en_biomass_chp,en_biomass_ccs,en_geothermal</t>
+  </si>
+  <si>
+    <t>IN607-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN607-765_IND</t>
+  </si>
+  <si>
+    <t>IN375-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN375-765_IND</t>
+  </si>
+  <si>
+    <t>w202980838-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w202980838-765_IND</t>
+  </si>
+  <si>
+    <t>w315824842-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w315824842-765_IND</t>
+  </si>
+  <si>
+    <t>w422204218-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w422204218-765_IND</t>
+  </si>
+  <si>
+    <t>w94199110-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w94199110-400_IND</t>
+  </si>
+  <si>
+    <t>w354062412-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w354062412-765_IND</t>
+  </si>
+  <si>
+    <t>w386018740-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w386018740-765_IND</t>
+  </si>
+  <si>
+    <t>w318090288-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w318090288-765_IND</t>
+  </si>
+  <si>
+    <t>IN317-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN317-400_IND</t>
+  </si>
+  <si>
+    <t>w311571096-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w311571096-765_IND</t>
+  </si>
+  <si>
+    <t>w545571850-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w545571850-765_IND</t>
+  </si>
+  <si>
+    <t>w521570801-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w521570801-765_IND</t>
+  </si>
+  <si>
+    <t>IN42-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN42-765_IND</t>
+  </si>
+  <si>
+    <t>w923365745-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w923365745-765_IND</t>
+  </si>
+  <si>
+    <t>w1074489047-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w1074489047-765_IND</t>
+  </si>
+  <si>
+    <t>w910151268-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w910151268-765_IND</t>
+  </si>
+  <si>
+    <t>w514344408-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w514344408-765_IND</t>
+  </si>
+  <si>
+    <t>IN267-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN267-765_IND</t>
+  </si>
+  <si>
+    <t>w311954703-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w311954703-765_IND</t>
+  </si>
+  <si>
+    <t>IN128-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN128-765_IND</t>
+  </si>
+  <si>
+    <t>IN578-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN578-765_IND</t>
+  </si>
+  <si>
+    <t>w1329624553-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w1329624553-765_IND</t>
+  </si>
+  <si>
+    <t>IN388-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN388-765_IND</t>
+  </si>
+  <si>
     <t>w319423421-765_IND</t>
   </si>
   <si>
     <t>at grid node - w319423421-765_IND</t>
   </si>
   <si>
-    <t>Bioenergy + CCUS,Bioenergy - Large scale unit,CCGT,CCGT + CCS,Coal + CCS,Gas turbine,IGCC,IGCC + CCS,Nuclear large,Oxyfuel + CCS,Steam Coal - SUBCRITICAL,Steam Coal - SUPERCRITICAL,Steam Coal - ULTRASUPERCRITICAL</t>
+    <t>IN94-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN94-765_IND</t>
+  </si>
+  <si>
+    <t>w1207477934-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w1207477934-765_IND</t>
+  </si>
+  <si>
+    <t>w698045832-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w698045832-765_IND</t>
+  </si>
+  <si>
+    <t>w420797421-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w420797421-765_IND</t>
+  </si>
+  <si>
+    <t>w408924420-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w408924420-765_IND</t>
+  </si>
+  <si>
+    <t>w492377703-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w492377703-765_IND</t>
+  </si>
+  <si>
+    <t>w423702239-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w423702239-765_IND</t>
+  </si>
+  <si>
+    <t>IN535-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN535-765_IND</t>
+  </si>
+  <si>
+    <t>IN412-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN412-765_IND</t>
+  </si>
+  <si>
+    <t>w118228036-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w118228036-400_IND</t>
+  </si>
+  <si>
+    <t>w408924427-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w408924427-765_IND</t>
+  </si>
+  <si>
+    <t>IN312-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN312-765_IND</t>
+  </si>
+  <si>
+    <t>w386153973-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w386153973-765_IND</t>
+  </si>
+  <si>
+    <t>w688672711-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w688672711-765_IND</t>
+  </si>
+  <si>
+    <t>w425401901-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w425401901-765_IND</t>
+  </si>
+  <si>
+    <t>w577176545-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w577176545-400_IND</t>
+  </si>
+  <si>
+    <t>w1015325412-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w1015325412-400_IND</t>
+  </si>
+  <si>
+    <t>w196933682-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w196933682-765_IND</t>
+  </si>
+  <si>
+    <t>w357515226-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w357515226-765_IND</t>
+  </si>
+  <si>
+    <t>IN325-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN325-400_IND</t>
+  </si>
+  <si>
+    <t>w248385304-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w248385304-765_IND</t>
+  </si>
+  <si>
+    <t>w205942950-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w205942950-400_IND</t>
+  </si>
+  <si>
+    <t>w311933111-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w311933111-765_IND</t>
   </si>
   <si>
     <t>w311176519-765_IND</t>
@@ -322,22 +610,178 @@
     <t>at grid node - w311176519-765_IND</t>
   </si>
   <si>
+    <t>w372701897-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w372701897-765_IND</t>
+  </si>
+  <si>
+    <t>IN748-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN748-765_IND</t>
+  </si>
+  <si>
+    <t>IN336-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN336-400_IND</t>
+  </si>
+  <si>
+    <t>w759521252-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w759521252-765_IND</t>
+  </si>
+  <si>
+    <t>w328548895-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w328548895-765_IND</t>
+  </si>
+  <si>
+    <t>w196563905-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w196563905-765_IND</t>
+  </si>
+  <si>
+    <t>w423166766-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w423166766-765_IND</t>
+  </si>
+  <si>
+    <t>w293597835-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w293597835-765_IND</t>
+  </si>
+  <si>
+    <t>w654736039-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w654736039-765_IND</t>
+  </si>
+  <si>
+    <t>w323266562-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w323266562-765_IND</t>
+  </si>
+  <si>
+    <t>w353914761-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w353914761-765_IND</t>
+  </si>
+  <si>
+    <t>w166692103-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w166692103-400_IND</t>
+  </si>
+  <si>
+    <t>w355560316-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w355560316-765_IND</t>
+  </si>
+  <si>
+    <t>w1206014676-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w1206014676-765_IND</t>
+  </si>
+  <si>
+    <t>w409158116-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w409158116-765_IND</t>
+  </si>
+  <si>
+    <t>IN529-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN529-765_IND</t>
+  </si>
+  <si>
+    <t>IN405-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN405-765_IND</t>
+  </si>
+  <si>
+    <t>w409798382-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w409798382-400_IND</t>
+  </si>
+  <si>
+    <t>w331275940-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w331275940-765_IND</t>
+  </si>
+  <si>
+    <t>IN399-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN399-765_IND</t>
+  </si>
+  <si>
+    <t>w192782338-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w192782338-765_IND</t>
+  </si>
+  <si>
+    <t>w353914865-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w353914865-765_IND</t>
+  </si>
+  <si>
+    <t>w209806650-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w209806650-400_IND</t>
+  </si>
+  <si>
+    <t>w247861059-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w247861059-765_IND</t>
+  </si>
+  <si>
+    <t>w417569420-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w417569420-765_IND</t>
+  </si>
+  <si>
+    <t>IN201-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN201-765_IND</t>
+  </si>
+  <si>
+    <t>w473902678-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w473902678-765_IND</t>
+  </si>
+  <si>
     <t>w429459345-765_IND</t>
   </si>
   <si>
     <t>at grid node - w429459345-765_IND</t>
   </si>
   <si>
-    <t>w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>w910151268-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w910151268-765_IND</t>
+    <t>IN121-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN121-765_IND</t>
   </si>
   <si>
     <t>w409112085-765_IND</t>
@@ -346,469 +790,37 @@
     <t>at grid node - w409112085-765_IND</t>
   </si>
   <si>
-    <t>w425401901-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w425401901-765_IND</t>
-  </si>
-  <si>
     <t>IN486-765_IND</t>
   </si>
   <si>
     <t>at grid node - IN486-765_IND</t>
   </si>
   <si>
-    <t>IN121-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN121-765_IND</t>
-  </si>
-  <si>
-    <t>w311571096-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w311571096-765_IND</t>
-  </si>
-  <si>
-    <t>w473902678-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w473902678-765_IND</t>
-  </si>
-  <si>
-    <t>IN201-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN201-765_IND</t>
-  </si>
-  <si>
-    <t>w417569420-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w417569420-765_IND</t>
-  </si>
-  <si>
-    <t>w1074489047-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w1074489047-765_IND</t>
-  </si>
-  <si>
-    <t>w247861059-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w247861059-765_IND</t>
-  </si>
-  <si>
-    <t>IN405-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN405-765_IND</t>
-  </si>
-  <si>
-    <t>IN325-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN325-400_IND</t>
-  </si>
-  <si>
-    <t>w1246177377-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w1246177377-765_IND</t>
-  </si>
-  <si>
-    <t>IN607-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN607-765_IND</t>
-  </si>
-  <si>
-    <t>IN375-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN375-765_IND</t>
-  </si>
-  <si>
-    <t>w202980838-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w202980838-765_IND</t>
-  </si>
-  <si>
-    <t>w315824842-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w315824842-765_IND</t>
-  </si>
-  <si>
-    <t>w422204218-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w422204218-765_IND</t>
-  </si>
-  <si>
-    <t>IN287-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN287-400_IND</t>
-  </si>
-  <si>
-    <t>w94199110-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w94199110-400_IND</t>
-  </si>
-  <si>
-    <t>w354062412-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w354062412-765_IND</t>
-  </si>
-  <si>
-    <t>w386018740-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w386018740-765_IND</t>
-  </si>
-  <si>
-    <t>w318090288-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w318090288-765_IND</t>
-  </si>
-  <si>
-    <t>IN317-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN317-400_IND</t>
-  </si>
-  <si>
-    <t>w545571850-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w545571850-765_IND</t>
-  </si>
-  <si>
-    <t>w521570801-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w521570801-765_IND</t>
-  </si>
-  <si>
-    <t>IN42-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN42-765_IND</t>
-  </si>
-  <si>
-    <t>w923365745-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w923365745-765_IND</t>
-  </si>
-  <si>
-    <t>w118228036-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w118228036-400_IND</t>
-  </si>
-  <si>
-    <t>w514344408-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w514344408-765_IND</t>
-  </si>
-  <si>
     <t>w688672798-765_IND</t>
   </si>
   <si>
     <t>at grid node - w688672798-765_IND</t>
   </si>
   <si>
-    <t>IN267-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN267-765_IND</t>
-  </si>
-  <si>
-    <t>w311954703-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w311954703-765_IND</t>
-  </si>
-  <si>
-    <t>IN128-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN128-765_IND</t>
-  </si>
-  <si>
-    <t>w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>IN578-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN578-765_IND</t>
-  </si>
-  <si>
-    <t>w1329624553-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w1329624553-765_IND</t>
-  </si>
-  <si>
-    <t>IN388-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN388-765_IND</t>
-  </si>
-  <si>
-    <t>w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>w1207477934-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w1207477934-765_IND</t>
-  </si>
-  <si>
-    <t>w698045832-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w698045832-765_IND</t>
-  </si>
-  <si>
-    <t>w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>w209806650-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w209806650-400_IND</t>
-  </si>
-  <si>
-    <t>w408924420-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w408924420-765_IND</t>
-  </si>
-  <si>
-    <t>w492377703-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w492377703-765_IND</t>
-  </si>
-  <si>
-    <t>w423702239-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w423702239-765_IND</t>
-  </si>
-  <si>
-    <t>IN535-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN535-765_IND</t>
-  </si>
-  <si>
-    <t>IN412-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN412-765_IND</t>
-  </si>
-  <si>
-    <t>IN94-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN94-765_IND</t>
-  </si>
-  <si>
-    <t>w408924427-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w408924427-765_IND</t>
-  </si>
-  <si>
-    <t>IN312-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN312-765_IND</t>
-  </si>
-  <si>
-    <t>w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>w409798382-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w409798382-400_IND</t>
-  </si>
-  <si>
-    <t>w192782338-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w192782338-765_IND</t>
-  </si>
-  <si>
-    <t>IN399-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN399-765_IND</t>
-  </si>
-  <si>
-    <t>w577176545-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w577176545-400_IND</t>
-  </si>
-  <si>
-    <t>w1015325412-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w1015325412-400_IND</t>
-  </si>
-  <si>
-    <t>w196933682-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w196933682-765_IND</t>
-  </si>
-  <si>
     <t>w105373531-765_IND</t>
   </si>
   <si>
     <t>at grid node - w105373531-765_IND</t>
   </si>
   <si>
-    <t>w357515226-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w357515226-765_IND</t>
-  </si>
-  <si>
-    <t>w248385304-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w248385304-765_IND</t>
-  </si>
-  <si>
-    <t>w205942950-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w205942950-400_IND</t>
-  </si>
-  <si>
-    <t>w311933111-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w311933111-765_IND</t>
-  </si>
-  <si>
-    <t>w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>IN748-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN748-765_IND</t>
-  </si>
-  <si>
-    <t>IN336-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN336-400_IND</t>
-  </si>
-  <si>
-    <t>w328548895-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w328548895-765_IND</t>
-  </si>
-  <si>
-    <t>w196563905-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w196563905-765_IND</t>
-  </si>
-  <si>
-    <t>w423166766-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w423166766-765_IND</t>
-  </si>
-  <si>
-    <t>w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>w654736039-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w654736039-765_IND</t>
-  </si>
-  <si>
-    <t>w323266562-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w323266562-765_IND</t>
-  </si>
-  <si>
-    <t>w353914761-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w353914761-765_IND</t>
-  </si>
-  <si>
-    <t>w166692103-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w166692103-400_IND</t>
-  </si>
-  <si>
-    <t>w355560316-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w355560316-765_IND</t>
-  </si>
-  <si>
-    <t>w1206014676-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w1206014676-765_IND</t>
-  </si>
-  <si>
-    <t>w409158116-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w409158116-765_IND</t>
-  </si>
-  <si>
-    <t>IN529-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN529-765_IND</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IND-1,EN_Hydro_IND-2,EN_Hydro_IND-3</t>
+    <t>w149822703-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w149822703-400_IND</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
+  </si>
+  <si>
+    <t>w1341291951-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w1341291951-765_IND</t>
   </si>
   <si>
     <t>IN10-765_IND</t>
@@ -829,12 +841,6 @@
     <t>at grid node - IN684-765_IND</t>
   </si>
   <si>
-    <t>w149822703-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w149822703-400_IND</t>
-  </si>
-  <si>
     <t>IN367-765_IND</t>
   </si>
   <si>
@@ -865,28 +871,322 @@
     <t>at grid node - IN263-400_IND</t>
   </si>
   <si>
+    <t>w375941438-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w375941438-400_IND</t>
+  </si>
+  <si>
+    <t>IN599-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN599-765_IND</t>
+  </si>
+  <si>
+    <t>IN583-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN583-765_IND</t>
+  </si>
+  <si>
+    <t>IN806-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN806-765_IND</t>
+  </si>
+  <si>
+    <t>IN808-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN808-765_IND</t>
+  </si>
+  <si>
+    <t>IN798-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN798-765_IND</t>
+  </si>
+  <si>
+    <t>IN488-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN488-765_IND</t>
+  </si>
+  <si>
+    <t>w375084335-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w375084335-400_IND</t>
+  </si>
+  <si>
+    <t>w439006823-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w439006823-400_IND</t>
+  </si>
+  <si>
+    <t>IN265-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN265-400_IND</t>
+  </si>
+  <si>
+    <t>w374367235-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w374367235-400_IND</t>
+  </si>
+  <si>
+    <t>w610646823-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w610646823-400_IND</t>
+  </si>
+  <si>
+    <t>IN155-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN155-400_IND</t>
+  </si>
+  <si>
+    <t>w315823978-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w315823978-765_IND</t>
+  </si>
+  <si>
+    <t>w116541259-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w116541259-400_IND</t>
+  </si>
+  <si>
+    <t>IN586-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN586-765_IND</t>
+  </si>
+  <si>
+    <t>w324059200-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w324059200-400_IND</t>
+  </si>
+  <si>
     <t>w1072445901-400_IND</t>
   </si>
   <si>
     <t>at grid node - w1072445901-400_IND</t>
   </si>
   <si>
-    <t>w375941438-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w375941438-400_IND</t>
-  </si>
-  <si>
-    <t>IN599-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN599-765_IND</t>
-  </si>
-  <si>
-    <t>w610646823-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w610646823-400_IND</t>
+    <t>w608461884-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w608461884-765_IND</t>
+  </si>
+  <si>
+    <t>w97392607-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w97392607-400_IND</t>
+  </si>
+  <si>
+    <t>IN742-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN742-765_IND</t>
+  </si>
+  <si>
+    <t>w1127651311-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w1127651311-765_IND</t>
+  </si>
+  <si>
+    <t>w245128370-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w245128370-765_IND</t>
+  </si>
+  <si>
+    <t>IN373-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN373-765_IND</t>
+  </si>
+  <si>
+    <t>w1001700959-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w1001700959-765_IND</t>
+  </si>
+  <si>
+    <t>IN187-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN187-765_IND</t>
+  </si>
+  <si>
+    <t>w453513742-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w453513742-765_IND</t>
+  </si>
+  <si>
+    <t>IN215-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN215-765_IND</t>
+  </si>
+  <si>
+    <t>w686891085-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w686891085-765_IND</t>
+  </si>
+  <si>
+    <t>w342204888-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w342204888-765_IND</t>
+  </si>
+  <si>
+    <t>IN205-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN205-765_IND</t>
+  </si>
+  <si>
+    <t>w1143180503-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w1143180503-765_IND</t>
+  </si>
+  <si>
+    <t>IN218-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN218-765_IND</t>
+  </si>
+  <si>
+    <t>IN148-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN148-765_IND</t>
+  </si>
+  <si>
+    <t>w631917408-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w631917408-765_IND</t>
+  </si>
+  <si>
+    <t>IN283-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN283-765_IND</t>
+  </si>
+  <si>
+    <t>w1078426593-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w1078426593-765_IND</t>
+  </si>
+  <si>
+    <t>IN292-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN292-765_IND</t>
+  </si>
+  <si>
+    <t>IN191-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN191-765_IND</t>
+  </si>
+  <si>
+    <t>w466424134-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w466424134-765_IND</t>
+  </si>
+  <si>
+    <t>IN246-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN246-765_IND</t>
+  </si>
+  <si>
+    <t>w209826798-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w209826798-765_IND</t>
+  </si>
+  <si>
+    <t>w315477169-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w315477169-765_IND</t>
+  </si>
+  <si>
+    <t>IN253-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN253-765_IND</t>
+  </si>
+  <si>
+    <t>IN803-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN803-765_IND</t>
+  </si>
+  <si>
+    <t>IN473-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN473-765_IND</t>
+  </si>
+  <si>
+    <t>IN476-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN476-765_IND</t>
+  </si>
+  <si>
+    <t>w318050929-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w318050929-765_IND</t>
+  </si>
+  <si>
+    <t>IN404-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN404-765_IND</t>
+  </si>
+  <si>
+    <t>w1336628403-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w1336628403-765_IND</t>
+  </si>
+  <si>
+    <t>IN275-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN275-765_IND</t>
+  </si>
+  <si>
+    <t>IN206-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN206-765_IND</t>
+  </si>
+  <si>
+    <t>IN199-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN199-765_IND</t>
   </si>
   <si>
     <t>IN685-765_IND</t>
@@ -895,82 +1195,10 @@
     <t>at grid node - IN685-765_IND</t>
   </si>
   <si>
-    <t>w324059200-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w324059200-400_IND</t>
-  </si>
-  <si>
-    <t>IN583-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN583-765_IND</t>
-  </si>
-  <si>
-    <t>IN586-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN586-765_IND</t>
-  </si>
-  <si>
-    <t>IN806-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN806-765_IND</t>
-  </si>
-  <si>
-    <t>IN808-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN808-765_IND</t>
-  </si>
-  <si>
-    <t>IN798-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN798-765_IND</t>
-  </si>
-  <si>
-    <t>IN488-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN488-765_IND</t>
-  </si>
-  <si>
-    <t>w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>w375084335-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w375084335-400_IND</t>
-  </si>
-  <si>
-    <t>w439006823-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w439006823-400_IND</t>
-  </si>
-  <si>
-    <t>IN265-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN265-400_IND</t>
-  </si>
-  <si>
-    <t>w608461884-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w608461884-765_IND</t>
-  </si>
-  <si>
-    <t>w374367235-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w374367235-400_IND</t>
+    <t>IN749-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN749-765_IND</t>
   </si>
   <si>
     <t>IN610-765_IND</t>
@@ -979,237 +1207,6 @@
     <t>at grid node - IN610-765_IND</t>
   </si>
   <si>
-    <t>IN155-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN155-400_IND</t>
-  </si>
-  <si>
-    <t>w97392607-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w97392607-400_IND</t>
-  </si>
-  <si>
-    <t>IN742-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN742-765_IND</t>
-  </si>
-  <si>
-    <t>w116541259-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w116541259-400_IND</t>
-  </si>
-  <si>
-    <t>w245128370-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w245128370-765_IND</t>
-  </si>
-  <si>
-    <t>IN749-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN749-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
-  </si>
-  <si>
-    <t>w1341291951-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w1341291951-765_IND</t>
-  </si>
-  <si>
-    <t>w1078426593-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w1078426593-765_IND</t>
-  </si>
-  <si>
-    <t>IN803-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN803-765_IND</t>
-  </si>
-  <si>
-    <t>IN473-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN473-765_IND</t>
-  </si>
-  <si>
-    <t>w453513742-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w453513742-765_IND</t>
-  </si>
-  <si>
-    <t>IN476-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN476-765_IND</t>
-  </si>
-  <si>
-    <t>w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>IN218-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN218-765_IND</t>
-  </si>
-  <si>
-    <t>w342204888-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w342204888-765_IND</t>
-  </si>
-  <si>
-    <t>w686891085-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w686891085-765_IND</t>
-  </si>
-  <si>
-    <t>IN148-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN148-765_IND</t>
-  </si>
-  <si>
-    <t>IN275-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN275-765_IND</t>
-  </si>
-  <si>
-    <t>IN191-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN191-765_IND</t>
-  </si>
-  <si>
-    <t>w466424134-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w466424134-765_IND</t>
-  </si>
-  <si>
-    <t>w631917408-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w631917408-765_IND</t>
-  </si>
-  <si>
-    <t>IN205-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN205-765_IND</t>
-  </si>
-  <si>
-    <t>IN404-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN404-765_IND</t>
-  </si>
-  <si>
-    <t>w315477169-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w315477169-765_IND</t>
-  </si>
-  <si>
-    <t>IN283-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN283-765_IND</t>
-  </si>
-  <si>
-    <t>w1001700959-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w1001700959-765_IND</t>
-  </si>
-  <si>
-    <t>w1336628403-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w1336628403-765_IND</t>
-  </si>
-  <si>
-    <t>w1127651311-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w1127651311-765_IND</t>
-  </si>
-  <si>
-    <t>IN187-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN187-765_IND</t>
-  </si>
-  <si>
-    <t>IN215-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN215-765_IND</t>
-  </si>
-  <si>
-    <t>IN199-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN199-765_IND</t>
-  </si>
-  <si>
-    <t>IN292-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN292-765_IND</t>
-  </si>
-  <si>
-    <t>IN253-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN253-765_IND</t>
-  </si>
-  <si>
-    <t>w318050929-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w318050929-765_IND</t>
-  </si>
-  <si>
-    <t>IN246-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN246-765_IND</t>
-  </si>
-  <si>
-    <t>w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>IN373-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN373-765_IND</t>
-  </si>
-  <si>
-    <t>IN206-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN206-765_IND</t>
-  </si>
-  <si>
     <t>IN180-765_IND</t>
   </si>
   <si>
@@ -1240,6 +1237,18 @@
     <t>at grid node - w311103617-765_IND</t>
   </si>
   <si>
+    <t>w801704865-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w801704865-765_IND</t>
+  </si>
+  <si>
+    <t>w840600239-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w840600239-765_IND</t>
+  </si>
+  <si>
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
@@ -1259,12 +1268,6 @@
   </si>
   <si>
     <t>at grid node - IN298-765_IND</t>
-  </si>
-  <si>
-    <t>w801704865-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w801704865-765_IND</t>
   </si>
   <si>
     <t>IN285-400_IND</t>
@@ -1634,15 +1637,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:T164"/>
+  <dimension ref="B3:O166"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -1650,7 +1653,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>59</v>
       </c>
@@ -1658,7 +1661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>85</v>
       </c>
@@ -1668,11 +1671,8 @@
       <c r="L9" t="s">
         <v>85</v>
       </c>
-      <c r="Q9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>33</v>
       </c>
@@ -1709,20 +1709,8 @@
       <c r="O10" t="s">
         <v>21</v>
       </c>
-      <c r="Q10" t="s">
-        <v>33</v>
-      </c>
-      <c r="R10" t="s">
-        <v>86</v>
-      </c>
-      <c r="S10" t="s">
-        <v>87</v>
-      </c>
-      <c r="T10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>88</v>
       </c>
@@ -1739,40 +1727,28 @@
         <v>88</v>
       </c>
       <c r="H11" t="s">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="I11" t="s">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="J11" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L11" t="s">
         <v>88</v>
       </c>
       <c r="M11" t="s">
-        <v>89</v>
+        <v>238</v>
       </c>
       <c r="N11" t="s">
-        <v>90</v>
+        <v>239</v>
       </c>
       <c r="O11" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>88</v>
-      </c>
-      <c r="R11" t="s">
-        <v>114</v>
-      </c>
-      <c r="S11" t="s">
-        <v>115</v>
-      </c>
-      <c r="T11" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>88</v>
       </c>
@@ -1789,40 +1765,28 @@
         <v>88</v>
       </c>
       <c r="H12" t="s">
-        <v>257</v>
+        <v>92</v>
       </c>
       <c r="I12" t="s">
-        <v>258</v>
+        <v>93</v>
       </c>
       <c r="J12" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L12" t="s">
         <v>88</v>
       </c>
       <c r="M12" t="s">
-        <v>92</v>
+        <v>242</v>
       </c>
       <c r="N12" t="s">
-        <v>93</v>
+        <v>243</v>
       </c>
       <c r="O12" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>88</v>
-      </c>
-      <c r="R12" t="s">
-        <v>110</v>
-      </c>
-      <c r="S12" t="s">
-        <v>111</v>
-      </c>
-      <c r="T12" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>88</v>
       </c>
@@ -1839,40 +1803,28 @@
         <v>88</v>
       </c>
       <c r="H13" t="s">
-        <v>188</v>
+        <v>94</v>
       </c>
       <c r="I13" t="s">
-        <v>189</v>
+        <v>95</v>
       </c>
       <c r="J13" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L13" t="s">
         <v>88</v>
       </c>
       <c r="M13" t="s">
-        <v>94</v>
+        <v>404</v>
       </c>
       <c r="N13" t="s">
-        <v>95</v>
+        <v>405</v>
       </c>
       <c r="O13" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>88</v>
-      </c>
-      <c r="R13" t="s">
-        <v>401</v>
-      </c>
-      <c r="S13" t="s">
-        <v>402</v>
-      </c>
-      <c r="T13" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>88</v>
       </c>
@@ -1889,40 +1841,28 @@
         <v>88</v>
       </c>
       <c r="H14" t="s">
-        <v>259</v>
+        <v>96</v>
       </c>
       <c r="I14" t="s">
-        <v>260</v>
+        <v>97</v>
       </c>
       <c r="J14" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L14" t="s">
         <v>88</v>
       </c>
       <c r="M14" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="O14" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>88</v>
-      </c>
-      <c r="R14" t="s">
-        <v>202</v>
-      </c>
-      <c r="S14" t="s">
-        <v>203</v>
-      </c>
-      <c r="T14" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>88</v>
       </c>
@@ -1939,40 +1879,28 @@
         <v>88</v>
       </c>
       <c r="H15" t="s">
-        <v>226</v>
+        <v>98</v>
       </c>
       <c r="I15" t="s">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="J15" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L15" t="s">
         <v>88</v>
       </c>
       <c r="M15" t="s">
-        <v>98</v>
+        <v>406</v>
       </c>
       <c r="N15" t="s">
-        <v>99</v>
+        <v>407</v>
       </c>
       <c r="O15" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>88</v>
-      </c>
-      <c r="R15" t="s">
         <v>403</v>
       </c>
-      <c r="S15" t="s">
-        <v>404</v>
-      </c>
-      <c r="T15" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>88</v>
       </c>
@@ -1989,40 +1917,28 @@
         <v>88</v>
       </c>
       <c r="H16" t="s">
-        <v>242</v>
+        <v>100</v>
       </c>
       <c r="I16" t="s">
-        <v>243</v>
+        <v>101</v>
       </c>
       <c r="J16" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L16" t="s">
         <v>88</v>
       </c>
       <c r="M16" t="s">
-        <v>100</v>
+        <v>226</v>
       </c>
       <c r="N16" t="s">
-        <v>101</v>
+        <v>227</v>
       </c>
       <c r="O16" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>88</v>
-      </c>
-      <c r="R16" t="s">
-        <v>96</v>
-      </c>
-      <c r="S16" t="s">
-        <v>97</v>
-      </c>
-      <c r="T16" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
         <v>88</v>
       </c>
@@ -2039,40 +1955,28 @@
         <v>88</v>
       </c>
       <c r="H17" t="s">
-        <v>261</v>
+        <v>102</v>
       </c>
       <c r="I17" t="s">
-        <v>262</v>
+        <v>103</v>
       </c>
       <c r="J17" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L17" t="s">
         <v>88</v>
       </c>
       <c r="M17" t="s">
-        <v>102</v>
+        <v>287</v>
       </c>
       <c r="N17" t="s">
-        <v>103</v>
+        <v>288</v>
       </c>
       <c r="O17" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>88</v>
-      </c>
-      <c r="R17" t="s">
-        <v>295</v>
-      </c>
-      <c r="S17" t="s">
-        <v>296</v>
-      </c>
-      <c r="T17" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>88</v>
       </c>
@@ -2089,40 +1993,28 @@
         <v>88</v>
       </c>
       <c r="H18" t="s">
-        <v>263</v>
+        <v>104</v>
       </c>
       <c r="I18" t="s">
-        <v>264</v>
+        <v>105</v>
       </c>
       <c r="J18" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L18" t="s">
         <v>88</v>
       </c>
       <c r="M18" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="N18" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="O18" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>88</v>
-      </c>
-      <c r="R18" t="s">
-        <v>98</v>
-      </c>
-      <c r="S18" t="s">
-        <v>99</v>
-      </c>
-      <c r="T18" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>88</v>
       </c>
@@ -2139,40 +2031,28 @@
         <v>88</v>
       </c>
       <c r="H19" t="s">
-        <v>265</v>
+        <v>106</v>
       </c>
       <c r="I19" t="s">
-        <v>266</v>
+        <v>107</v>
       </c>
       <c r="J19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L19" t="s">
         <v>88</v>
       </c>
       <c r="M19" t="s">
-        <v>106</v>
+        <v>408</v>
       </c>
       <c r="N19" t="s">
-        <v>107</v>
+        <v>409</v>
       </c>
       <c r="O19" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>88</v>
-      </c>
-      <c r="R19" t="s">
-        <v>405</v>
-      </c>
-      <c r="S19" t="s">
-        <v>406</v>
-      </c>
-      <c r="T19" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
         <v>88</v>
       </c>
@@ -2189,40 +2069,28 @@
         <v>88</v>
       </c>
       <c r="H20" t="s">
-        <v>267</v>
+        <v>108</v>
       </c>
       <c r="I20" t="s">
-        <v>268</v>
+        <v>109</v>
       </c>
       <c r="J20" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L20" t="s">
         <v>88</v>
       </c>
       <c r="M20" t="s">
-        <v>108</v>
+        <v>399</v>
       </c>
       <c r="N20" t="s">
-        <v>109</v>
+        <v>400</v>
       </c>
       <c r="O20" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>88</v>
-      </c>
-      <c r="R20" t="s">
-        <v>407</v>
-      </c>
-      <c r="S20" t="s">
-        <v>408</v>
-      </c>
-      <c r="T20" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
         <v>88</v>
       </c>
@@ -2245,34 +2113,22 @@
         <v>111</v>
       </c>
       <c r="J21" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L21" t="s">
         <v>88</v>
       </c>
       <c r="M21" t="s">
-        <v>110</v>
+        <v>410</v>
       </c>
       <c r="N21" t="s">
-        <v>111</v>
+        <v>411</v>
       </c>
       <c r="O21" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>88</v>
-      </c>
-      <c r="R21" t="s">
-        <v>409</v>
-      </c>
-      <c r="S21" t="s">
-        <v>410</v>
-      </c>
-      <c r="T21" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
         <v>88</v>
       </c>
@@ -2289,40 +2145,28 @@
         <v>88</v>
       </c>
       <c r="H22" t="s">
-        <v>269</v>
+        <v>112</v>
       </c>
       <c r="I22" t="s">
-        <v>270</v>
+        <v>113</v>
       </c>
       <c r="J22" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L22" t="s">
         <v>88</v>
       </c>
       <c r="M22" t="s">
-        <v>326</v>
+        <v>170</v>
       </c>
       <c r="N22" t="s">
-        <v>327</v>
+        <v>171</v>
       </c>
       <c r="O22" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>88</v>
-      </c>
-      <c r="R22" t="s">
-        <v>102</v>
-      </c>
-      <c r="S22" t="s">
-        <v>103</v>
-      </c>
-      <c r="T22" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
         <v>88</v>
       </c>
@@ -2339,40 +2183,28 @@
         <v>88</v>
       </c>
       <c r="H23" t="s">
-        <v>228</v>
+        <v>114</v>
       </c>
       <c r="I23" t="s">
-        <v>229</v>
+        <v>115</v>
       </c>
       <c r="J23" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L23" t="s">
         <v>88</v>
       </c>
       <c r="M23" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N23" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O23" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>88</v>
-      </c>
-      <c r="R23" t="s">
-        <v>226</v>
-      </c>
-      <c r="S23" t="s">
-        <v>227</v>
-      </c>
-      <c r="T23" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
         <v>88</v>
       </c>
@@ -2389,40 +2221,28 @@
         <v>88</v>
       </c>
       <c r="H24" t="s">
-        <v>252</v>
+        <v>116</v>
       </c>
       <c r="I24" t="s">
-        <v>253</v>
+        <v>117</v>
       </c>
       <c r="J24" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L24" t="s">
         <v>88</v>
       </c>
       <c r="M24" t="s">
-        <v>112</v>
+        <v>412</v>
       </c>
       <c r="N24" t="s">
-        <v>113</v>
+        <v>413</v>
       </c>
       <c r="O24" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>88</v>
-      </c>
-      <c r="R24" t="s">
-        <v>411</v>
-      </c>
-      <c r="S24" t="s">
-        <v>412</v>
-      </c>
-      <c r="T24" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>88</v>
       </c>
@@ -2439,40 +2259,28 @@
         <v>88</v>
       </c>
       <c r="H25" t="s">
-        <v>271</v>
+        <v>118</v>
       </c>
       <c r="I25" t="s">
-        <v>272</v>
+        <v>119</v>
       </c>
       <c r="J25" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L25" t="s">
         <v>88</v>
       </c>
       <c r="M25" t="s">
-        <v>114</v>
+        <v>359</v>
       </c>
       <c r="N25" t="s">
-        <v>115</v>
+        <v>360</v>
       </c>
       <c r="O25" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>88</v>
-      </c>
-      <c r="R25" t="s">
-        <v>338</v>
-      </c>
-      <c r="S25" t="s">
-        <v>339</v>
-      </c>
-      <c r="T25" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
         <v>88</v>
       </c>
@@ -2489,40 +2297,28 @@
         <v>88</v>
       </c>
       <c r="H26" t="s">
-        <v>273</v>
+        <v>120</v>
       </c>
       <c r="I26" t="s">
-        <v>274</v>
+        <v>121</v>
       </c>
       <c r="J26" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L26" t="s">
         <v>88</v>
       </c>
       <c r="M26" t="s">
-        <v>116</v>
+        <v>244</v>
       </c>
       <c r="N26" t="s">
-        <v>117</v>
+        <v>245</v>
       </c>
       <c r="O26" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>88</v>
-      </c>
-      <c r="R26" t="s">
-        <v>94</v>
-      </c>
-      <c r="S26" t="s">
-        <v>95</v>
-      </c>
-      <c r="T26" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
         <v>88</v>
       </c>
@@ -2539,40 +2335,28 @@
         <v>88</v>
       </c>
       <c r="H27" t="s">
-        <v>275</v>
+        <v>122</v>
       </c>
       <c r="I27" t="s">
-        <v>276</v>
+        <v>123</v>
       </c>
       <c r="J27" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L27" t="s">
         <v>88</v>
       </c>
       <c r="M27" t="s">
-        <v>118</v>
+        <v>214</v>
       </c>
       <c r="N27" t="s">
-        <v>119</v>
+        <v>215</v>
       </c>
       <c r="O27" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>88</v>
-      </c>
-      <c r="R27" t="s">
-        <v>248</v>
-      </c>
-      <c r="S27" t="s">
-        <v>249</v>
-      </c>
-      <c r="T27" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
         <v>88</v>
       </c>
@@ -2589,40 +2373,28 @@
         <v>88</v>
       </c>
       <c r="H28" t="s">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="I28" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="J28" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L28" t="s">
         <v>88</v>
       </c>
       <c r="M28" t="s">
-        <v>120</v>
+        <v>414</v>
       </c>
       <c r="N28" t="s">
-        <v>121</v>
+        <v>415</v>
       </c>
       <c r="O28" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>88</v>
-      </c>
-      <c r="R28" t="s">
-        <v>413</v>
-      </c>
-      <c r="S28" t="s">
-        <v>414</v>
-      </c>
-      <c r="T28" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
         <v>88</v>
       </c>
@@ -2639,40 +2411,28 @@
         <v>88</v>
       </c>
       <c r="H29" t="s">
-        <v>277</v>
+        <v>126</v>
       </c>
       <c r="I29" t="s">
-        <v>278</v>
+        <v>127</v>
       </c>
       <c r="J29" t="s">
+        <v>258</v>
+      </c>
+      <c r="L29" t="s">
+        <v>88</v>
+      </c>
+      <c r="M29" t="s">
         <v>256</v>
       </c>
-      <c r="L29" t="s">
-        <v>88</v>
-      </c>
-      <c r="M29" t="s">
-        <v>122</v>
-      </c>
       <c r="N29" t="s">
-        <v>123</v>
+        <v>257</v>
       </c>
       <c r="O29" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>88</v>
-      </c>
-      <c r="R29" t="s">
-        <v>263</v>
-      </c>
-      <c r="S29" t="s">
-        <v>264</v>
-      </c>
-      <c r="T29" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
         <v>88</v>
       </c>
@@ -2689,40 +2449,28 @@
         <v>88</v>
       </c>
       <c r="H30" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="I30" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="J30" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L30" t="s">
         <v>88</v>
       </c>
       <c r="M30" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="N30" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="O30" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>88</v>
-      </c>
-      <c r="R30" t="s">
-        <v>154</v>
-      </c>
-      <c r="S30" t="s">
-        <v>155</v>
-      </c>
-      <c r="T30" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
         <v>88</v>
       </c>
@@ -2739,40 +2487,28 @@
         <v>88</v>
       </c>
       <c r="H31" t="s">
-        <v>248</v>
+        <v>130</v>
       </c>
       <c r="I31" t="s">
-        <v>249</v>
+        <v>131</v>
       </c>
       <c r="J31" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L31" t="s">
         <v>88</v>
       </c>
       <c r="M31" t="s">
-        <v>126</v>
+        <v>218</v>
       </c>
       <c r="N31" t="s">
-        <v>127</v>
+        <v>219</v>
       </c>
       <c r="O31" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>88</v>
-      </c>
-      <c r="R31" t="s">
-        <v>252</v>
-      </c>
-      <c r="S31" t="s">
-        <v>253</v>
-      </c>
-      <c r="T31" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
         <v>88</v>
       </c>
@@ -2789,40 +2525,28 @@
         <v>88</v>
       </c>
       <c r="H32" t="s">
-        <v>279</v>
+        <v>132</v>
       </c>
       <c r="I32" t="s">
-        <v>280</v>
+        <v>133</v>
       </c>
       <c r="J32" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L32" t="s">
         <v>88</v>
       </c>
       <c r="M32" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="N32" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="O32" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>88</v>
-      </c>
-      <c r="R32" t="s">
-        <v>186</v>
-      </c>
-      <c r="S32" t="s">
-        <v>187</v>
-      </c>
-      <c r="T32" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
         <v>88</v>
       </c>
@@ -2839,40 +2563,28 @@
         <v>88</v>
       </c>
       <c r="H33" t="s">
-        <v>281</v>
+        <v>134</v>
       </c>
       <c r="I33" t="s">
-        <v>282</v>
+        <v>135</v>
       </c>
       <c r="J33" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L33" t="s">
         <v>88</v>
       </c>
       <c r="M33" t="s">
-        <v>130</v>
+        <v>303</v>
       </c>
       <c r="N33" t="s">
-        <v>131</v>
+        <v>304</v>
       </c>
       <c r="O33" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>88</v>
-      </c>
-      <c r="R33" t="s">
-        <v>299</v>
-      </c>
-      <c r="S33" t="s">
-        <v>300</v>
-      </c>
-      <c r="T33" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
         <v>88</v>
       </c>
@@ -2889,40 +2601,28 @@
         <v>88</v>
       </c>
       <c r="H34" t="s">
-        <v>283</v>
+        <v>136</v>
       </c>
       <c r="I34" t="s">
-        <v>284</v>
+        <v>137</v>
       </c>
       <c r="J34" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L34" t="s">
         <v>88</v>
       </c>
       <c r="M34" t="s">
-        <v>132</v>
+        <v>416</v>
       </c>
       <c r="N34" t="s">
-        <v>133</v>
+        <v>417</v>
       </c>
       <c r="O34" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>88</v>
-      </c>
-      <c r="R34" t="s">
-        <v>415</v>
-      </c>
-      <c r="S34" t="s">
-        <v>416</v>
-      </c>
-      <c r="T34" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
         <v>88</v>
       </c>
@@ -2939,40 +2639,28 @@
         <v>88</v>
       </c>
       <c r="H35" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="I35" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="J35" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L35" t="s">
         <v>88</v>
       </c>
       <c r="M35" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="N35" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="O35" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>88</v>
-      </c>
-      <c r="R35" t="s">
-        <v>164</v>
-      </c>
-      <c r="S35" t="s">
-        <v>165</v>
-      </c>
-      <c r="T35" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="36" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
         <v>88</v>
       </c>
@@ -2989,40 +2677,28 @@
         <v>88</v>
       </c>
       <c r="H36" t="s">
-        <v>285</v>
+        <v>140</v>
       </c>
       <c r="I36" t="s">
-        <v>286</v>
+        <v>141</v>
       </c>
       <c r="J36" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L36" t="s">
         <v>88</v>
       </c>
       <c r="M36" t="s">
-        <v>136</v>
+        <v>319</v>
       </c>
       <c r="N36" t="s">
-        <v>137</v>
+        <v>320</v>
       </c>
       <c r="O36" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>88</v>
-      </c>
-      <c r="R36" t="s">
-        <v>368</v>
-      </c>
-      <c r="S36" t="s">
-        <v>369</v>
-      </c>
-      <c r="T36" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
         <v>88</v>
       </c>
@@ -3039,40 +2715,28 @@
         <v>88</v>
       </c>
       <c r="H37" t="s">
-        <v>287</v>
+        <v>142</v>
       </c>
       <c r="I37" t="s">
-        <v>288</v>
+        <v>143</v>
       </c>
       <c r="J37" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L37" t="s">
         <v>88</v>
       </c>
       <c r="M37" t="s">
-        <v>138</v>
+        <v>313</v>
       </c>
       <c r="N37" t="s">
-        <v>139</v>
+        <v>314</v>
       </c>
       <c r="O37" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>88</v>
-      </c>
-      <c r="R37" t="s">
-        <v>307</v>
-      </c>
-      <c r="S37" t="s">
-        <v>308</v>
-      </c>
-      <c r="T37" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
         <v>88</v>
       </c>
@@ -3089,40 +2753,28 @@
         <v>88</v>
       </c>
       <c r="H38" t="s">
-        <v>289</v>
+        <v>144</v>
       </c>
       <c r="I38" t="s">
-        <v>290</v>
+        <v>145</v>
       </c>
       <c r="J38" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L38" t="s">
         <v>88</v>
       </c>
       <c r="M38" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="N38" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="O38" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>88</v>
-      </c>
-      <c r="R38" t="s">
-        <v>148</v>
-      </c>
-      <c r="S38" t="s">
-        <v>149</v>
-      </c>
-      <c r="T38" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
         <v>88</v>
       </c>
@@ -3139,40 +2791,28 @@
         <v>88</v>
       </c>
       <c r="H39" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="I39" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="J39" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L39" t="s">
         <v>88</v>
       </c>
       <c r="M39" t="s">
-        <v>142</v>
+        <v>418</v>
       </c>
       <c r="N39" t="s">
-        <v>143</v>
+        <v>419</v>
       </c>
       <c r="O39" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>88</v>
-      </c>
-      <c r="R39" t="s">
-        <v>417</v>
-      </c>
-      <c r="S39" t="s">
-        <v>418</v>
-      </c>
-      <c r="T39" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
         <v>88</v>
       </c>
@@ -3189,40 +2829,28 @@
         <v>88</v>
       </c>
       <c r="H40" t="s">
-        <v>291</v>
+        <v>148</v>
       </c>
       <c r="I40" t="s">
-        <v>292</v>
+        <v>149</v>
       </c>
       <c r="J40" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L40" t="s">
         <v>88</v>
       </c>
       <c r="M40" t="s">
-        <v>144</v>
+        <v>420</v>
       </c>
       <c r="N40" t="s">
-        <v>145</v>
+        <v>421</v>
       </c>
       <c r="O40" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>88</v>
-      </c>
-      <c r="R40" t="s">
-        <v>419</v>
-      </c>
-      <c r="S40" t="s">
-        <v>420</v>
-      </c>
-      <c r="T40" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
         <v>88</v>
       </c>
@@ -3239,40 +2867,28 @@
         <v>88</v>
       </c>
       <c r="H41" t="s">
-        <v>293</v>
+        <v>150</v>
       </c>
       <c r="I41" t="s">
-        <v>294</v>
+        <v>151</v>
       </c>
       <c r="J41" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L41" t="s">
         <v>88</v>
       </c>
       <c r="M41" t="s">
-        <v>146</v>
+        <v>422</v>
       </c>
       <c r="N41" t="s">
-        <v>147</v>
+        <v>423</v>
       </c>
       <c r="O41" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>88</v>
-      </c>
-      <c r="R41" t="s">
-        <v>421</v>
-      </c>
-      <c r="S41" t="s">
-        <v>422</v>
-      </c>
-      <c r="T41" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
         <v>88</v>
       </c>
@@ -3289,40 +2905,28 @@
         <v>88</v>
       </c>
       <c r="H42" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="I42" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="J42" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L42" t="s">
         <v>88</v>
       </c>
       <c r="M42" t="s">
-        <v>148</v>
+        <v>269</v>
       </c>
       <c r="N42" t="s">
-        <v>149</v>
+        <v>270</v>
       </c>
       <c r="O42" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>88</v>
-      </c>
-      <c r="R42" t="s">
-        <v>267</v>
-      </c>
-      <c r="S42" t="s">
-        <v>268</v>
-      </c>
-      <c r="T42" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
         <v>88</v>
       </c>
@@ -3339,40 +2943,28 @@
         <v>88</v>
       </c>
       <c r="H43" t="s">
-        <v>295</v>
+        <v>154</v>
       </c>
       <c r="I43" t="s">
-        <v>296</v>
+        <v>155</v>
       </c>
       <c r="J43" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L43" t="s">
         <v>88</v>
       </c>
       <c r="M43" t="s">
-        <v>150</v>
+        <v>261</v>
       </c>
       <c r="N43" t="s">
-        <v>151</v>
+        <v>262</v>
       </c>
       <c r="O43" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>88</v>
-      </c>
-      <c r="R43" t="s">
-        <v>257</v>
-      </c>
-      <c r="S43" t="s">
-        <v>258</v>
-      </c>
-      <c r="T43" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
         <v>88</v>
       </c>
@@ -3389,40 +2981,28 @@
         <v>88</v>
       </c>
       <c r="H44" t="s">
-        <v>297</v>
+        <v>156</v>
       </c>
       <c r="I44" t="s">
-        <v>298</v>
+        <v>157</v>
       </c>
       <c r="J44" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L44" t="s">
         <v>88</v>
       </c>
       <c r="M44" t="s">
-        <v>152</v>
+        <v>277</v>
       </c>
       <c r="N44" t="s">
-        <v>153</v>
+        <v>278</v>
       </c>
       <c r="O44" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>88</v>
-      </c>
-      <c r="R44" t="s">
-        <v>277</v>
-      </c>
-      <c r="S44" t="s">
-        <v>278</v>
-      </c>
-      <c r="T44" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
         <v>88</v>
       </c>
@@ -3439,40 +3019,28 @@
         <v>88</v>
       </c>
       <c r="H45" t="s">
-        <v>299</v>
+        <v>158</v>
       </c>
       <c r="I45" t="s">
-        <v>300</v>
+        <v>159</v>
       </c>
       <c r="J45" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L45" t="s">
         <v>88</v>
       </c>
       <c r="M45" t="s">
-        <v>154</v>
+        <v>248</v>
       </c>
       <c r="N45" t="s">
-        <v>155</v>
+        <v>249</v>
       </c>
       <c r="O45" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>88</v>
-      </c>
-      <c r="R45" t="s">
-        <v>100</v>
-      </c>
-      <c r="S45" t="s">
-        <v>101</v>
-      </c>
-      <c r="T45" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
         <v>88</v>
       </c>
@@ -3489,28 +3057,16 @@
         <v>88</v>
       </c>
       <c r="H46" t="s">
-        <v>301</v>
+        <v>160</v>
       </c>
       <c r="I46" t="s">
-        <v>302</v>
+        <v>161</v>
       </c>
       <c r="J46" t="s">
-        <v>256</v>
-      </c>
-      <c r="L46" t="s">
-        <v>88</v>
-      </c>
-      <c r="M46" t="s">
-        <v>156</v>
-      </c>
-      <c r="N46" t="s">
-        <v>157</v>
-      </c>
-      <c r="O46" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
         <v>88</v>
       </c>
@@ -3527,28 +3083,16 @@
         <v>88</v>
       </c>
       <c r="H47" t="s">
-        <v>214</v>
+        <v>162</v>
       </c>
       <c r="I47" t="s">
-        <v>215</v>
+        <v>163</v>
       </c>
       <c r="J47" t="s">
-        <v>256</v>
-      </c>
-      <c r="L47" t="s">
-        <v>88</v>
-      </c>
-      <c r="M47" t="s">
-        <v>158</v>
-      </c>
-      <c r="N47" t="s">
-        <v>159</v>
-      </c>
-      <c r="O47" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
         <v>88</v>
       </c>
@@ -3565,28 +3109,16 @@
         <v>88</v>
       </c>
       <c r="H48" t="s">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="I48" t="s">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="J48" t="s">
-        <v>256</v>
-      </c>
-      <c r="L48" t="s">
-        <v>88</v>
-      </c>
-      <c r="M48" t="s">
-        <v>160</v>
-      </c>
-      <c r="N48" t="s">
-        <v>161</v>
-      </c>
-      <c r="O48" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
         <v>88</v>
       </c>
@@ -3603,28 +3135,16 @@
         <v>88</v>
       </c>
       <c r="H49" t="s">
-        <v>303</v>
+        <v>166</v>
       </c>
       <c r="I49" t="s">
-        <v>304</v>
+        <v>167</v>
       </c>
       <c r="J49" t="s">
-        <v>256</v>
-      </c>
-      <c r="L49" t="s">
-        <v>88</v>
-      </c>
-      <c r="M49" t="s">
-        <v>162</v>
-      </c>
-      <c r="N49" t="s">
-        <v>163</v>
-      </c>
-      <c r="O49" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
         <v>88</v>
       </c>
@@ -3641,28 +3161,16 @@
         <v>88</v>
       </c>
       <c r="H50" t="s">
-        <v>305</v>
+        <v>168</v>
       </c>
       <c r="I50" t="s">
-        <v>306</v>
+        <v>169</v>
       </c>
       <c r="J50" t="s">
-        <v>256</v>
-      </c>
-      <c r="L50" t="s">
-        <v>88</v>
-      </c>
-      <c r="M50" t="s">
-        <v>164</v>
-      </c>
-      <c r="N50" t="s">
-        <v>165</v>
-      </c>
-      <c r="O50" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
         <v>88</v>
       </c>
@@ -3679,28 +3187,16 @@
         <v>88</v>
       </c>
       <c r="H51" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="I51" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="J51" t="s">
-        <v>256</v>
-      </c>
-      <c r="L51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M51" t="s">
-        <v>166</v>
-      </c>
-      <c r="N51" t="s">
-        <v>167</v>
-      </c>
-      <c r="O51" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
         <v>88</v>
       </c>
@@ -3717,28 +3213,16 @@
         <v>88</v>
       </c>
       <c r="H52" t="s">
-        <v>307</v>
+        <v>172</v>
       </c>
       <c r="I52" t="s">
-        <v>308</v>
+        <v>173</v>
       </c>
       <c r="J52" t="s">
-        <v>256</v>
-      </c>
-      <c r="L52" t="s">
-        <v>88</v>
-      </c>
-      <c r="M52" t="s">
-        <v>168</v>
-      </c>
-      <c r="N52" t="s">
-        <v>169</v>
-      </c>
-      <c r="O52" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
         <v>88</v>
       </c>
@@ -3755,28 +3239,16 @@
         <v>88</v>
       </c>
       <c r="H53" t="s">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="I53" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="J53" t="s">
-        <v>256</v>
-      </c>
-      <c r="L53" t="s">
-        <v>88</v>
-      </c>
-      <c r="M53" t="s">
-        <v>170</v>
-      </c>
-      <c r="N53" t="s">
-        <v>171</v>
-      </c>
-      <c r="O53" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
         <v>88</v>
       </c>
@@ -3793,28 +3265,16 @@
         <v>88</v>
       </c>
       <c r="H54" t="s">
-        <v>309</v>
+        <v>176</v>
       </c>
       <c r="I54" t="s">
-        <v>310</v>
+        <v>177</v>
       </c>
       <c r="J54" t="s">
-        <v>256</v>
-      </c>
-      <c r="L54" t="s">
-        <v>88</v>
-      </c>
-      <c r="M54" t="s">
-        <v>172</v>
-      </c>
-      <c r="N54" t="s">
-        <v>173</v>
-      </c>
-      <c r="O54" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="55" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
         <v>88</v>
       </c>
@@ -3831,28 +3291,16 @@
         <v>88</v>
       </c>
       <c r="H55" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="I55" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="J55" t="s">
-        <v>256</v>
-      </c>
-      <c r="L55" t="s">
-        <v>88</v>
-      </c>
-      <c r="M55" t="s">
-        <v>174</v>
-      </c>
-      <c r="N55" t="s">
-        <v>175</v>
-      </c>
-      <c r="O55" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="56" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
         <v>88</v>
       </c>
@@ -3869,28 +3317,16 @@
         <v>88</v>
       </c>
       <c r="H56" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="I56" t="s">
-        <v>312</v>
+        <v>181</v>
       </c>
       <c r="J56" t="s">
-        <v>256</v>
-      </c>
-      <c r="L56" t="s">
-        <v>88</v>
-      </c>
-      <c r="M56" t="s">
-        <v>176</v>
-      </c>
-      <c r="N56" t="s">
-        <v>177</v>
-      </c>
-      <c r="O56" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="57" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
         <v>88</v>
       </c>
@@ -3907,28 +3343,16 @@
         <v>88</v>
       </c>
       <c r="H57" t="s">
-        <v>313</v>
+        <v>182</v>
       </c>
       <c r="I57" t="s">
-        <v>314</v>
+        <v>183</v>
       </c>
       <c r="J57" t="s">
-        <v>256</v>
-      </c>
-      <c r="L57" t="s">
-        <v>88</v>
-      </c>
-      <c r="M57" t="s">
-        <v>178</v>
-      </c>
-      <c r="N57" t="s">
-        <v>179</v>
-      </c>
-      <c r="O57" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="58" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
         <v>88</v>
       </c>
@@ -3945,28 +3369,16 @@
         <v>88</v>
       </c>
       <c r="H58" t="s">
-        <v>315</v>
+        <v>184</v>
       </c>
       <c r="I58" t="s">
-        <v>316</v>
+        <v>185</v>
       </c>
       <c r="J58" t="s">
-        <v>256</v>
-      </c>
-      <c r="L58" t="s">
-        <v>88</v>
-      </c>
-      <c r="M58" t="s">
-        <v>180</v>
-      </c>
-      <c r="N58" t="s">
-        <v>181</v>
-      </c>
-      <c r="O58" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="59" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
         <v>88</v>
       </c>
@@ -3989,22 +3401,10 @@
         <v>187</v>
       </c>
       <c r="J59" t="s">
-        <v>256</v>
-      </c>
-      <c r="L59" t="s">
-        <v>88</v>
-      </c>
-      <c r="M59" t="s">
-        <v>182</v>
-      </c>
-      <c r="N59" t="s">
-        <v>183</v>
-      </c>
-      <c r="O59" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="60" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
         <v>88</v>
       </c>
@@ -4021,28 +3421,16 @@
         <v>88</v>
       </c>
       <c r="H60" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="I60" t="s">
-        <v>127</v>
+        <v>189</v>
       </c>
       <c r="J60" t="s">
-        <v>256</v>
-      </c>
-      <c r="L60" t="s">
-        <v>88</v>
-      </c>
-      <c r="M60" t="s">
-        <v>184</v>
-      </c>
-      <c r="N60" t="s">
-        <v>185</v>
-      </c>
-      <c r="O60" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="61" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
         <v>88</v>
       </c>
@@ -4059,28 +3447,16 @@
         <v>88</v>
       </c>
       <c r="H61" t="s">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="I61" t="s">
-        <v>251</v>
+        <v>191</v>
       </c>
       <c r="J61" t="s">
-        <v>256</v>
-      </c>
-      <c r="L61" t="s">
-        <v>88</v>
-      </c>
-      <c r="M61" t="s">
-        <v>186</v>
-      </c>
-      <c r="N61" t="s">
-        <v>187</v>
-      </c>
-      <c r="O61" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="62" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
         <v>88</v>
       </c>
@@ -4097,28 +3473,16 @@
         <v>88</v>
       </c>
       <c r="H62" t="s">
-        <v>254</v>
+        <v>192</v>
       </c>
       <c r="I62" t="s">
-        <v>255</v>
+        <v>193</v>
       </c>
       <c r="J62" t="s">
-        <v>256</v>
-      </c>
-      <c r="L62" t="s">
-        <v>88</v>
-      </c>
-      <c r="M62" t="s">
-        <v>190</v>
-      </c>
-      <c r="N62" t="s">
-        <v>191</v>
-      </c>
-      <c r="O62" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="63" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
         <v>88</v>
       </c>
@@ -4135,28 +3499,16 @@
         <v>88</v>
       </c>
       <c r="H63" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="I63" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="J63" t="s">
-        <v>256</v>
-      </c>
-      <c r="L63" t="s">
-        <v>88</v>
-      </c>
-      <c r="M63" t="s">
-        <v>192</v>
-      </c>
-      <c r="N63" t="s">
-        <v>193</v>
-      </c>
-      <c r="O63" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="64" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
         <v>88</v>
       </c>
@@ -4173,28 +3525,16 @@
         <v>88</v>
       </c>
       <c r="H64" t="s">
-        <v>317</v>
+        <v>196</v>
       </c>
       <c r="I64" t="s">
-        <v>318</v>
+        <v>197</v>
       </c>
       <c r="J64" t="s">
-        <v>256</v>
-      </c>
-      <c r="L64" t="s">
-        <v>88</v>
-      </c>
-      <c r="M64" t="s">
-        <v>194</v>
-      </c>
-      <c r="N64" t="s">
-        <v>195</v>
-      </c>
-      <c r="O64" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
         <v>88</v>
       </c>
@@ -4211,28 +3551,16 @@
         <v>88</v>
       </c>
       <c r="H65" t="s">
-        <v>319</v>
+        <v>198</v>
       </c>
       <c r="I65" t="s">
-        <v>320</v>
+        <v>199</v>
       </c>
       <c r="J65" t="s">
-        <v>256</v>
-      </c>
-      <c r="L65" t="s">
-        <v>88</v>
-      </c>
-      <c r="M65" t="s">
-        <v>196</v>
-      </c>
-      <c r="N65" t="s">
-        <v>197</v>
-      </c>
-      <c r="O65" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
         <v>88</v>
       </c>
@@ -4249,28 +3577,16 @@
         <v>88</v>
       </c>
       <c r="H66" t="s">
-        <v>96</v>
+        <v>200</v>
       </c>
       <c r="I66" t="s">
-        <v>97</v>
+        <v>201</v>
       </c>
       <c r="J66" t="s">
-        <v>256</v>
-      </c>
-      <c r="L66" t="s">
-        <v>88</v>
-      </c>
-      <c r="M66" t="s">
-        <v>198</v>
-      </c>
-      <c r="N66" t="s">
-        <v>199</v>
-      </c>
-      <c r="O66" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
         <v>88</v>
       </c>
@@ -4287,28 +3603,16 @@
         <v>88</v>
       </c>
       <c r="H67" t="s">
-        <v>321</v>
+        <v>202</v>
       </c>
       <c r="I67" t="s">
-        <v>322</v>
+        <v>203</v>
       </c>
       <c r="J67" t="s">
-        <v>256</v>
-      </c>
-      <c r="L67" t="s">
-        <v>88</v>
-      </c>
-      <c r="M67" t="s">
-        <v>200</v>
-      </c>
-      <c r="N67" t="s">
-        <v>201</v>
-      </c>
-      <c r="O67" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
         <v>88</v>
       </c>
@@ -4325,28 +3629,16 @@
         <v>88</v>
       </c>
       <c r="H68" t="s">
-        <v>323</v>
+        <v>204</v>
       </c>
       <c r="I68" t="s">
-        <v>324</v>
+        <v>205</v>
       </c>
       <c r="J68" t="s">
-        <v>256</v>
-      </c>
-      <c r="L68" t="s">
-        <v>88</v>
-      </c>
-      <c r="M68" t="s">
-        <v>202</v>
-      </c>
-      <c r="N68" t="s">
-        <v>203</v>
-      </c>
-      <c r="O68" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
         <v>88</v>
       </c>
@@ -4359,20 +3651,20 @@
       <c r="E69" t="s">
         <v>91</v>
       </c>
-      <c r="L69" t="s">
-        <v>88</v>
-      </c>
-      <c r="M69" t="s">
-        <v>204</v>
-      </c>
-      <c r="N69" t="s">
-        <v>205</v>
-      </c>
-      <c r="O69" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G69" t="s">
+        <v>88</v>
+      </c>
+      <c r="H69" t="s">
+        <v>206</v>
+      </c>
+      <c r="I69" t="s">
+        <v>207</v>
+      </c>
+      <c r="J69" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
         <v>88</v>
       </c>
@@ -4385,20 +3677,20 @@
       <c r="E70" t="s">
         <v>91</v>
       </c>
-      <c r="L70" t="s">
-        <v>88</v>
-      </c>
-      <c r="M70" t="s">
-        <v>206</v>
-      </c>
-      <c r="N70" t="s">
-        <v>207</v>
-      </c>
-      <c r="O70" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G70" t="s">
+        <v>88</v>
+      </c>
+      <c r="H70" t="s">
+        <v>208</v>
+      </c>
+      <c r="I70" t="s">
+        <v>209</v>
+      </c>
+      <c r="J70" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
         <v>88</v>
       </c>
@@ -4411,20 +3703,20 @@
       <c r="E71" t="s">
         <v>91</v>
       </c>
-      <c r="L71" t="s">
-        <v>88</v>
-      </c>
-      <c r="M71" t="s">
-        <v>208</v>
-      </c>
-      <c r="N71" t="s">
-        <v>209</v>
-      </c>
-      <c r="O71" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G71" t="s">
+        <v>88</v>
+      </c>
+      <c r="H71" t="s">
+        <v>210</v>
+      </c>
+      <c r="I71" t="s">
+        <v>211</v>
+      </c>
+      <c r="J71" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
         <v>88</v>
       </c>
@@ -4437,20 +3729,20 @@
       <c r="E72" t="s">
         <v>91</v>
       </c>
-      <c r="L72" t="s">
-        <v>88</v>
-      </c>
-      <c r="M72" t="s">
-        <v>210</v>
-      </c>
-      <c r="N72" t="s">
-        <v>211</v>
-      </c>
-      <c r="O72" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G72" t="s">
+        <v>88</v>
+      </c>
+      <c r="H72" t="s">
+        <v>212</v>
+      </c>
+      <c r="I72" t="s">
+        <v>213</v>
+      </c>
+      <c r="J72" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
         <v>88</v>
       </c>
@@ -4463,20 +3755,20 @@
       <c r="E73" t="s">
         <v>91</v>
       </c>
-      <c r="L73" t="s">
-        <v>88</v>
-      </c>
-      <c r="M73" t="s">
-        <v>212</v>
-      </c>
-      <c r="N73" t="s">
-        <v>213</v>
-      </c>
-      <c r="O73" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G73" t="s">
+        <v>88</v>
+      </c>
+      <c r="H73" t="s">
+        <v>214</v>
+      </c>
+      <c r="I73" t="s">
+        <v>215</v>
+      </c>
+      <c r="J73" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
         <v>88</v>
       </c>
@@ -4489,20 +3781,20 @@
       <c r="E74" t="s">
         <v>91</v>
       </c>
-      <c r="L74" t="s">
-        <v>88</v>
-      </c>
-      <c r="M74" t="s">
-        <v>214</v>
-      </c>
-      <c r="N74" t="s">
-        <v>215</v>
-      </c>
-      <c r="O74" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G74" t="s">
+        <v>88</v>
+      </c>
+      <c r="H74" t="s">
+        <v>216</v>
+      </c>
+      <c r="I74" t="s">
+        <v>217</v>
+      </c>
+      <c r="J74" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
         <v>88</v>
       </c>
@@ -4515,20 +3807,20 @@
       <c r="E75" t="s">
         <v>91</v>
       </c>
-      <c r="L75" t="s">
-        <v>88</v>
-      </c>
-      <c r="M75" t="s">
-        <v>216</v>
-      </c>
-      <c r="N75" t="s">
-        <v>217</v>
-      </c>
-      <c r="O75" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G75" t="s">
+        <v>88</v>
+      </c>
+      <c r="H75" t="s">
+        <v>218</v>
+      </c>
+      <c r="I75" t="s">
+        <v>219</v>
+      </c>
+      <c r="J75" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
         <v>88</v>
       </c>
@@ -4541,20 +3833,20 @@
       <c r="E76" t="s">
         <v>91</v>
       </c>
-      <c r="L76" t="s">
-        <v>88</v>
-      </c>
-      <c r="M76" t="s">
-        <v>218</v>
-      </c>
-      <c r="N76" t="s">
-        <v>219</v>
-      </c>
-      <c r="O76" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G76" t="s">
+        <v>88</v>
+      </c>
+      <c r="H76" t="s">
+        <v>220</v>
+      </c>
+      <c r="I76" t="s">
+        <v>221</v>
+      </c>
+      <c r="J76" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
         <v>88</v>
       </c>
@@ -4567,20 +3859,20 @@
       <c r="E77" t="s">
         <v>91</v>
       </c>
-      <c r="L77" t="s">
-        <v>88</v>
-      </c>
-      <c r="M77" t="s">
-        <v>220</v>
-      </c>
-      <c r="N77" t="s">
-        <v>221</v>
-      </c>
-      <c r="O77" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="78" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G77" t="s">
+        <v>88</v>
+      </c>
+      <c r="H77" t="s">
+        <v>222</v>
+      </c>
+      <c r="I77" t="s">
+        <v>223</v>
+      </c>
+      <c r="J77" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
         <v>88</v>
       </c>
@@ -4593,20 +3885,20 @@
       <c r="E78" t="s">
         <v>91</v>
       </c>
-      <c r="L78" t="s">
-        <v>88</v>
-      </c>
-      <c r="M78" t="s">
-        <v>222</v>
-      </c>
-      <c r="N78" t="s">
-        <v>223</v>
-      </c>
-      <c r="O78" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G78" t="s">
+        <v>88</v>
+      </c>
+      <c r="H78" t="s">
+        <v>224</v>
+      </c>
+      <c r="I78" t="s">
+        <v>225</v>
+      </c>
+      <c r="J78" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
         <v>88</v>
       </c>
@@ -4619,20 +3911,20 @@
       <c r="E79" t="s">
         <v>91</v>
       </c>
-      <c r="L79" t="s">
-        <v>88</v>
-      </c>
-      <c r="M79" t="s">
-        <v>224</v>
-      </c>
-      <c r="N79" t="s">
-        <v>225</v>
-      </c>
-      <c r="O79" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G79" t="s">
+        <v>88</v>
+      </c>
+      <c r="H79" t="s">
+        <v>226</v>
+      </c>
+      <c r="I79" t="s">
+        <v>227</v>
+      </c>
+      <c r="J79" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
         <v>88</v>
       </c>
@@ -4645,20 +3937,20 @@
       <c r="E80" t="s">
         <v>91</v>
       </c>
-      <c r="L80" t="s">
-        <v>88</v>
-      </c>
-      <c r="M80" t="s">
-        <v>226</v>
-      </c>
-      <c r="N80" t="s">
-        <v>227</v>
-      </c>
-      <c r="O80" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="81" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G80" t="s">
+        <v>88</v>
+      </c>
+      <c r="H80" t="s">
+        <v>228</v>
+      </c>
+      <c r="I80" t="s">
+        <v>229</v>
+      </c>
+      <c r="J80" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
         <v>88</v>
       </c>
@@ -4671,20 +3963,20 @@
       <c r="E81" t="s">
         <v>91</v>
       </c>
-      <c r="L81" t="s">
-        <v>88</v>
-      </c>
-      <c r="M81" t="s">
-        <v>228</v>
-      </c>
-      <c r="N81" t="s">
-        <v>229</v>
-      </c>
-      <c r="O81" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="82" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G81" t="s">
+        <v>88</v>
+      </c>
+      <c r="H81" t="s">
+        <v>230</v>
+      </c>
+      <c r="I81" t="s">
+        <v>231</v>
+      </c>
+      <c r="J81" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
         <v>88</v>
       </c>
@@ -4697,20 +3989,20 @@
       <c r="E82" t="s">
         <v>91</v>
       </c>
-      <c r="L82" t="s">
-        <v>88</v>
-      </c>
-      <c r="M82" t="s">
-        <v>230</v>
-      </c>
-      <c r="N82" t="s">
-        <v>231</v>
-      </c>
-      <c r="O82" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="83" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G82" t="s">
+        <v>88</v>
+      </c>
+      <c r="H82" t="s">
+        <v>232</v>
+      </c>
+      <c r="I82" t="s">
+        <v>233</v>
+      </c>
+      <c r="J82" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B83" t="s">
         <v>88</v>
       </c>
@@ -4723,20 +4015,20 @@
       <c r="E83" t="s">
         <v>91</v>
       </c>
-      <c r="L83" t="s">
-        <v>88</v>
-      </c>
-      <c r="M83" t="s">
-        <v>232</v>
-      </c>
-      <c r="N83" t="s">
-        <v>233</v>
-      </c>
-      <c r="O83" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="84" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G83" t="s">
+        <v>88</v>
+      </c>
+      <c r="H83" t="s">
+        <v>234</v>
+      </c>
+      <c r="I83" t="s">
+        <v>235</v>
+      </c>
+      <c r="J83" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B84" t="s">
         <v>88</v>
       </c>
@@ -4749,20 +4041,20 @@
       <c r="E84" t="s">
         <v>91</v>
       </c>
-      <c r="L84" t="s">
-        <v>88</v>
-      </c>
-      <c r="M84" t="s">
-        <v>234</v>
-      </c>
-      <c r="N84" t="s">
-        <v>235</v>
-      </c>
-      <c r="O84" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="85" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G84" t="s">
+        <v>88</v>
+      </c>
+      <c r="H84" t="s">
+        <v>259</v>
+      </c>
+      <c r="I84" t="s">
+        <v>260</v>
+      </c>
+      <c r="J84" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
         <v>88</v>
       </c>
@@ -4775,20 +4067,20 @@
       <c r="E85" t="s">
         <v>91</v>
       </c>
-      <c r="L85" t="s">
-        <v>88</v>
-      </c>
-      <c r="M85" t="s">
+      <c r="G85" t="s">
+        <v>88</v>
+      </c>
+      <c r="H85" t="s">
         <v>236</v>
       </c>
-      <c r="N85" t="s">
+      <c r="I85" t="s">
         <v>237</v>
       </c>
-      <c r="O85" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="86" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J85" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B86" t="s">
         <v>88</v>
       </c>
@@ -4801,20 +4093,20 @@
       <c r="E86" t="s">
         <v>91</v>
       </c>
-      <c r="L86" t="s">
-        <v>88</v>
-      </c>
-      <c r="M86" t="s">
+      <c r="G86" t="s">
+        <v>88</v>
+      </c>
+      <c r="H86" t="s">
         <v>238</v>
       </c>
-      <c r="N86" t="s">
+      <c r="I86" t="s">
         <v>239</v>
       </c>
-      <c r="O86" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="87" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J86" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B87" t="s">
         <v>88</v>
       </c>
@@ -4827,20 +4119,20 @@
       <c r="E87" t="s">
         <v>91</v>
       </c>
-      <c r="L87" t="s">
-        <v>88</v>
-      </c>
-      <c r="M87" t="s">
+      <c r="G87" t="s">
+        <v>88</v>
+      </c>
+      <c r="H87" t="s">
         <v>240</v>
       </c>
-      <c r="N87" t="s">
+      <c r="I87" t="s">
         <v>241</v>
       </c>
-      <c r="O87" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="88" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J87" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B88" t="s">
         <v>88</v>
       </c>
@@ -4853,20 +4145,20 @@
       <c r="E88" t="s">
         <v>91</v>
       </c>
-      <c r="L88" t="s">
-        <v>88</v>
-      </c>
-      <c r="M88" t="s">
+      <c r="G88" t="s">
+        <v>88</v>
+      </c>
+      <c r="H88" t="s">
         <v>242</v>
       </c>
-      <c r="N88" t="s">
+      <c r="I88" t="s">
         <v>243</v>
       </c>
-      <c r="O88" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="89" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J88" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B89" t="s">
         <v>88</v>
       </c>
@@ -4879,20 +4171,20 @@
       <c r="E89" t="s">
         <v>91</v>
       </c>
-      <c r="L89" t="s">
-        <v>88</v>
-      </c>
-      <c r="M89" t="s">
+      <c r="G89" t="s">
+        <v>88</v>
+      </c>
+      <c r="H89" t="s">
         <v>244</v>
       </c>
-      <c r="N89" t="s">
+      <c r="I89" t="s">
         <v>245</v>
       </c>
-      <c r="O89" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="90" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J89" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B90" t="s">
         <v>88</v>
       </c>
@@ -4905,20 +4197,20 @@
       <c r="E90" t="s">
         <v>91</v>
       </c>
-      <c r="L90" t="s">
-        <v>88</v>
-      </c>
-      <c r="M90" t="s">
+      <c r="G90" t="s">
+        <v>88</v>
+      </c>
+      <c r="H90" t="s">
         <v>246</v>
       </c>
-      <c r="N90" t="s">
+      <c r="I90" t="s">
         <v>247</v>
       </c>
-      <c r="O90" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="91" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J90" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B91" t="s">
         <v>88</v>
       </c>
@@ -4931,20 +4223,20 @@
       <c r="E91" t="s">
         <v>91</v>
       </c>
-      <c r="L91" t="s">
-        <v>88</v>
-      </c>
-      <c r="M91" t="s">
+      <c r="G91" t="s">
+        <v>88</v>
+      </c>
+      <c r="H91" t="s">
         <v>248</v>
       </c>
-      <c r="N91" t="s">
+      <c r="I91" t="s">
         <v>249</v>
       </c>
-      <c r="O91" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="92" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J91" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B92" t="s">
         <v>88</v>
       </c>
@@ -4957,20 +4249,20 @@
       <c r="E92" t="s">
         <v>91</v>
       </c>
-      <c r="L92" t="s">
-        <v>88</v>
-      </c>
-      <c r="M92" t="s">
+      <c r="G92" t="s">
+        <v>88</v>
+      </c>
+      <c r="H92" t="s">
         <v>250</v>
       </c>
-      <c r="N92" t="s">
+      <c r="I92" t="s">
         <v>251</v>
       </c>
-      <c r="O92" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="93" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J92" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B93" t="s">
         <v>88</v>
       </c>
@@ -4983,1011 +4275,1051 @@
       <c r="E93" t="s">
         <v>91</v>
       </c>
-      <c r="L93" t="s">
-        <v>88</v>
-      </c>
-      <c r="M93" t="s">
+      <c r="G93" t="s">
+        <v>88</v>
+      </c>
+      <c r="H93" t="s">
+        <v>261</v>
+      </c>
+      <c r="I93" t="s">
+        <v>262</v>
+      </c>
+      <c r="J93" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B94" t="s">
+        <v>88</v>
+      </c>
+      <c r="C94" t="s">
+        <v>256</v>
+      </c>
+      <c r="D94" t="s">
+        <v>257</v>
+      </c>
+      <c r="E94" t="s">
+        <v>91</v>
+      </c>
+      <c r="G94" t="s">
+        <v>88</v>
+      </c>
+      <c r="H94" t="s">
+        <v>263</v>
+      </c>
+      <c r="I94" t="s">
+        <v>264</v>
+      </c>
+      <c r="J94" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G95" t="s">
+        <v>88</v>
+      </c>
+      <c r="H95" t="s">
+        <v>265</v>
+      </c>
+      <c r="I95" t="s">
+        <v>266</v>
+      </c>
+      <c r="J95" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G96" t="s">
+        <v>88</v>
+      </c>
+      <c r="H96" t="s">
+        <v>256</v>
+      </c>
+      <c r="I96" t="s">
+        <v>257</v>
+      </c>
+      <c r="J96" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="97" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G97" t="s">
+        <v>88</v>
+      </c>
+      <c r="H97" t="s">
+        <v>267</v>
+      </c>
+      <c r="I97" t="s">
+        <v>268</v>
+      </c>
+      <c r="J97" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="98" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G98" t="s">
+        <v>88</v>
+      </c>
+      <c r="H98" t="s">
+        <v>269</v>
+      </c>
+      <c r="I98" t="s">
+        <v>270</v>
+      </c>
+      <c r="J98" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="99" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G99" t="s">
+        <v>88</v>
+      </c>
+      <c r="H99" t="s">
+        <v>271</v>
+      </c>
+      <c r="I99" t="s">
+        <v>272</v>
+      </c>
+      <c r="J99" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="100" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G100" t="s">
+        <v>88</v>
+      </c>
+      <c r="H100" t="s">
+        <v>273</v>
+      </c>
+      <c r="I100" t="s">
+        <v>274</v>
+      </c>
+      <c r="J100" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="101" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G101" t="s">
+        <v>88</v>
+      </c>
+      <c r="H101" t="s">
+        <v>275</v>
+      </c>
+      <c r="I101" t="s">
+        <v>276</v>
+      </c>
+      <c r="J101" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="102" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G102" t="s">
+        <v>88</v>
+      </c>
+      <c r="H102" t="s">
+        <v>277</v>
+      </c>
+      <c r="I102" t="s">
+        <v>278</v>
+      </c>
+      <c r="J102" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="103" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G103" t="s">
+        <v>88</v>
+      </c>
+      <c r="H103" t="s">
+        <v>279</v>
+      </c>
+      <c r="I103" t="s">
+        <v>280</v>
+      </c>
+      <c r="J103" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="104" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G104" t="s">
+        <v>88</v>
+      </c>
+      <c r="H104" t="s">
+        <v>281</v>
+      </c>
+      <c r="I104" t="s">
+        <v>282</v>
+      </c>
+      <c r="J104" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="105" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G105" t="s">
+        <v>88</v>
+      </c>
+      <c r="H105" t="s">
+        <v>283</v>
+      </c>
+      <c r="I105" t="s">
+        <v>284</v>
+      </c>
+      <c r="J105" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="106" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G106" t="s">
+        <v>88</v>
+      </c>
+      <c r="H106" t="s">
+        <v>285</v>
+      </c>
+      <c r="I106" t="s">
+        <v>286</v>
+      </c>
+      <c r="J106" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="107" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G107" t="s">
+        <v>88</v>
+      </c>
+      <c r="H107" t="s">
+        <v>287</v>
+      </c>
+      <c r="I107" t="s">
+        <v>288</v>
+      </c>
+      <c r="J107" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="108" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G108" t="s">
+        <v>88</v>
+      </c>
+      <c r="H108" t="s">
+        <v>289</v>
+      </c>
+      <c r="I108" t="s">
+        <v>290</v>
+      </c>
+      <c r="J108" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="109" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G109" t="s">
+        <v>88</v>
+      </c>
+      <c r="H109" t="s">
+        <v>291</v>
+      </c>
+      <c r="I109" t="s">
+        <v>292</v>
+      </c>
+      <c r="J109" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="110" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G110" t="s">
+        <v>88</v>
+      </c>
+      <c r="H110" t="s">
+        <v>293</v>
+      </c>
+      <c r="I110" t="s">
+        <v>294</v>
+      </c>
+      <c r="J110" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="111" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G111" t="s">
+        <v>88</v>
+      </c>
+      <c r="H111" t="s">
+        <v>295</v>
+      </c>
+      <c r="I111" t="s">
+        <v>296</v>
+      </c>
+      <c r="J111" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="112" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G112" t="s">
+        <v>88</v>
+      </c>
+      <c r="H112" t="s">
+        <v>297</v>
+      </c>
+      <c r="I112" t="s">
+        <v>298</v>
+      </c>
+      <c r="J112" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="113" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G113" t="s">
+        <v>88</v>
+      </c>
+      <c r="H113" t="s">
+        <v>299</v>
+      </c>
+      <c r="I113" t="s">
+        <v>300</v>
+      </c>
+      <c r="J113" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="114" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G114" t="s">
+        <v>88</v>
+      </c>
+      <c r="H114" t="s">
+        <v>301</v>
+      </c>
+      <c r="I114" t="s">
+        <v>302</v>
+      </c>
+      <c r="J114" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="115" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G115" t="s">
+        <v>88</v>
+      </c>
+      <c r="H115" t="s">
+        <v>303</v>
+      </c>
+      <c r="I115" t="s">
+        <v>304</v>
+      </c>
+      <c r="J115" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="116" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G116" t="s">
+        <v>88</v>
+      </c>
+      <c r="H116" t="s">
+        <v>305</v>
+      </c>
+      <c r="I116" t="s">
+        <v>306</v>
+      </c>
+      <c r="J116" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="117" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G117" t="s">
+        <v>88</v>
+      </c>
+      <c r="H117" t="s">
+        <v>307</v>
+      </c>
+      <c r="I117" t="s">
+        <v>308</v>
+      </c>
+      <c r="J117" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="118" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G118" t="s">
+        <v>88</v>
+      </c>
+      <c r="H118" t="s">
+        <v>309</v>
+      </c>
+      <c r="I118" t="s">
+        <v>310</v>
+      </c>
+      <c r="J118" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="119" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G119" t="s">
+        <v>88</v>
+      </c>
+      <c r="H119" t="s">
+        <v>311</v>
+      </c>
+      <c r="I119" t="s">
+        <v>312</v>
+      </c>
+      <c r="J119" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="120" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G120" t="s">
+        <v>88</v>
+      </c>
+      <c r="H120" t="s">
+        <v>313</v>
+      </c>
+      <c r="I120" t="s">
+        <v>314</v>
+      </c>
+      <c r="J120" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="121" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G121" t="s">
+        <v>88</v>
+      </c>
+      <c r="H121" t="s">
+        <v>315</v>
+      </c>
+      <c r="I121" t="s">
+        <v>316</v>
+      </c>
+      <c r="J121" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="122" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G122" t="s">
+        <v>88</v>
+      </c>
+      <c r="H122" t="s">
+        <v>317</v>
+      </c>
+      <c r="I122" t="s">
+        <v>318</v>
+      </c>
+      <c r="J122" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="123" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G123" t="s">
+        <v>88</v>
+      </c>
+      <c r="H123" t="s">
+        <v>319</v>
+      </c>
+      <c r="I123" t="s">
+        <v>320</v>
+      </c>
+      <c r="J123" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="124" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G124" t="s">
+        <v>88</v>
+      </c>
+      <c r="H124" t="s">
+        <v>321</v>
+      </c>
+      <c r="I124" t="s">
+        <v>322</v>
+      </c>
+      <c r="J124" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="125" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G125" t="s">
+        <v>88</v>
+      </c>
+      <c r="H125" t="s">
+        <v>323</v>
+      </c>
+      <c r="I125" t="s">
+        <v>324</v>
+      </c>
+      <c r="J125" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="126" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G126" t="s">
+        <v>88</v>
+      </c>
+      <c r="H126" t="s">
+        <v>325</v>
+      </c>
+      <c r="I126" t="s">
+        <v>326</v>
+      </c>
+      <c r="J126" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="127" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G127" t="s">
+        <v>88</v>
+      </c>
+      <c r="H127" t="s">
+        <v>327</v>
+      </c>
+      <c r="I127" t="s">
+        <v>328</v>
+      </c>
+      <c r="J127" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="128" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G128" t="s">
+        <v>88</v>
+      </c>
+      <c r="H128" t="s">
+        <v>329</v>
+      </c>
+      <c r="I128" t="s">
+        <v>330</v>
+      </c>
+      <c r="J128" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="129" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G129" t="s">
+        <v>88</v>
+      </c>
+      <c r="H129" t="s">
+        <v>331</v>
+      </c>
+      <c r="I129" t="s">
+        <v>332</v>
+      </c>
+      <c r="J129" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="130" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G130" t="s">
+        <v>88</v>
+      </c>
+      <c r="H130" t="s">
+        <v>333</v>
+      </c>
+      <c r="I130" t="s">
+        <v>334</v>
+      </c>
+      <c r="J130" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="131" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G131" t="s">
+        <v>88</v>
+      </c>
+      <c r="H131" t="s">
+        <v>335</v>
+      </c>
+      <c r="I131" t="s">
+        <v>336</v>
+      </c>
+      <c r="J131" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="132" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G132" t="s">
+        <v>88</v>
+      </c>
+      <c r="H132" t="s">
+        <v>337</v>
+      </c>
+      <c r="I132" t="s">
+        <v>338</v>
+      </c>
+      <c r="J132" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="133" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G133" t="s">
+        <v>88</v>
+      </c>
+      <c r="H133" t="s">
+        <v>339</v>
+      </c>
+      <c r="I133" t="s">
+        <v>340</v>
+      </c>
+      <c r="J133" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="134" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G134" t="s">
+        <v>88</v>
+      </c>
+      <c r="H134" t="s">
+        <v>341</v>
+      </c>
+      <c r="I134" t="s">
+        <v>342</v>
+      </c>
+      <c r="J134" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="135" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G135" t="s">
+        <v>88</v>
+      </c>
+      <c r="H135" t="s">
+        <v>343</v>
+      </c>
+      <c r="I135" t="s">
+        <v>344</v>
+      </c>
+      <c r="J135" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="136" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G136" t="s">
+        <v>88</v>
+      </c>
+      <c r="H136" t="s">
+        <v>345</v>
+      </c>
+      <c r="I136" t="s">
+        <v>346</v>
+      </c>
+      <c r="J136" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="137" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G137" t="s">
+        <v>88</v>
+      </c>
+      <c r="H137" t="s">
+        <v>347</v>
+      </c>
+      <c r="I137" t="s">
+        <v>348</v>
+      </c>
+      <c r="J137" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="138" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G138" t="s">
+        <v>88</v>
+      </c>
+      <c r="H138" t="s">
+        <v>349</v>
+      </c>
+      <c r="I138" t="s">
+        <v>350</v>
+      </c>
+      <c r="J138" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="139" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G139" t="s">
+        <v>88</v>
+      </c>
+      <c r="H139" t="s">
+        <v>351</v>
+      </c>
+      <c r="I139" t="s">
+        <v>352</v>
+      </c>
+      <c r="J139" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="140" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G140" t="s">
+        <v>88</v>
+      </c>
+      <c r="H140" t="s">
+        <v>353</v>
+      </c>
+      <c r="I140" t="s">
+        <v>354</v>
+      </c>
+      <c r="J140" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="141" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G141" t="s">
+        <v>88</v>
+      </c>
+      <c r="H141" t="s">
+        <v>355</v>
+      </c>
+      <c r="I141" t="s">
+        <v>356</v>
+      </c>
+      <c r="J141" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="142" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G142" t="s">
+        <v>88</v>
+      </c>
+      <c r="H142" t="s">
+        <v>357</v>
+      </c>
+      <c r="I142" t="s">
+        <v>358</v>
+      </c>
+      <c r="J142" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="143" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G143" t="s">
+        <v>88</v>
+      </c>
+      <c r="H143" t="s">
+        <v>359</v>
+      </c>
+      <c r="I143" t="s">
+        <v>360</v>
+      </c>
+      <c r="J143" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="144" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G144" t="s">
+        <v>88</v>
+      </c>
+      <c r="H144" t="s">
+        <v>361</v>
+      </c>
+      <c r="I144" t="s">
+        <v>362</v>
+      </c>
+      <c r="J144" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="145" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G145" t="s">
+        <v>88</v>
+      </c>
+      <c r="H145" t="s">
+        <v>363</v>
+      </c>
+      <c r="I145" t="s">
+        <v>364</v>
+      </c>
+      <c r="J145" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="146" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G146" t="s">
+        <v>88</v>
+      </c>
+      <c r="H146" t="s">
         <v>252</v>
       </c>
-      <c r="N93" t="s">
+      <c r="I146" t="s">
         <v>253</v>
       </c>
-      <c r="O93" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="94" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L94" t="s">
-        <v>88</v>
-      </c>
-      <c r="M94" t="s">
+      <c r="J146" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="147" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G147" t="s">
+        <v>88</v>
+      </c>
+      <c r="H147" t="s">
+        <v>365</v>
+      </c>
+      <c r="I147" t="s">
+        <v>366</v>
+      </c>
+      <c r="J147" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="148" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G148" t="s">
+        <v>88</v>
+      </c>
+      <c r="H148" t="s">
+        <v>367</v>
+      </c>
+      <c r="I148" t="s">
+        <v>368</v>
+      </c>
+      <c r="J148" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="149" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G149" t="s">
+        <v>88</v>
+      </c>
+      <c r="H149" t="s">
+        <v>369</v>
+      </c>
+      <c r="I149" t="s">
+        <v>370</v>
+      </c>
+      <c r="J149" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="150" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G150" t="s">
+        <v>88</v>
+      </c>
+      <c r="H150" t="s">
+        <v>371</v>
+      </c>
+      <c r="I150" t="s">
+        <v>372</v>
+      </c>
+      <c r="J150" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="151" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G151" t="s">
+        <v>88</v>
+      </c>
+      <c r="H151" t="s">
+        <v>373</v>
+      </c>
+      <c r="I151" t="s">
+        <v>374</v>
+      </c>
+      <c r="J151" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="152" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G152" t="s">
+        <v>88</v>
+      </c>
+      <c r="H152" t="s">
+        <v>375</v>
+      </c>
+      <c r="I152" t="s">
+        <v>376</v>
+      </c>
+      <c r="J152" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="153" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G153" t="s">
+        <v>88</v>
+      </c>
+      <c r="H153" t="s">
+        <v>377</v>
+      </c>
+      <c r="I153" t="s">
+        <v>378</v>
+      </c>
+      <c r="J153" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="154" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G154" t="s">
+        <v>88</v>
+      </c>
+      <c r="H154" t="s">
+        <v>379</v>
+      </c>
+      <c r="I154" t="s">
+        <v>380</v>
+      </c>
+      <c r="J154" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="155" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G155" t="s">
+        <v>88</v>
+      </c>
+      <c r="H155" t="s">
+        <v>381</v>
+      </c>
+      <c r="I155" t="s">
+        <v>382</v>
+      </c>
+      <c r="J155" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="156" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G156" t="s">
+        <v>88</v>
+      </c>
+      <c r="H156" t="s">
+        <v>383</v>
+      </c>
+      <c r="I156" t="s">
+        <v>384</v>
+      </c>
+      <c r="J156" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="157" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G157" t="s">
+        <v>88</v>
+      </c>
+      <c r="H157" t="s">
+        <v>385</v>
+      </c>
+      <c r="I157" t="s">
+        <v>386</v>
+      </c>
+      <c r="J157" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="158" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G158" t="s">
+        <v>88</v>
+      </c>
+      <c r="H158" t="s">
         <v>254</v>
       </c>
-      <c r="N94" t="s">
+      <c r="I158" t="s">
         <v>255</v>
       </c>
-      <c r="O94" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="95" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L95" t="s">
-        <v>88</v>
-      </c>
-      <c r="M95" t="s">
-        <v>328</v>
-      </c>
-      <c r="N95" t="s">
-        <v>329</v>
-      </c>
-      <c r="O95" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="96" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L96" t="s">
-        <v>88</v>
-      </c>
-      <c r="M96" t="s">
-        <v>299</v>
-      </c>
-      <c r="N96" t="s">
-        <v>300</v>
-      </c>
-      <c r="O96" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="97" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L97" t="s">
-        <v>88</v>
-      </c>
-      <c r="M97" t="s">
-        <v>295</v>
-      </c>
-      <c r="N97" t="s">
-        <v>296</v>
-      </c>
-      <c r="O97" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="98" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L98" t="s">
-        <v>88</v>
-      </c>
-      <c r="M98" t="s">
-        <v>330</v>
-      </c>
-      <c r="N98" t="s">
-        <v>331</v>
-      </c>
-      <c r="O98" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="99" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L99" t="s">
-        <v>88</v>
-      </c>
-      <c r="M99" t="s">
-        <v>291</v>
-      </c>
-      <c r="N99" t="s">
-        <v>292</v>
-      </c>
-      <c r="O99" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="100" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L100" t="s">
-        <v>88</v>
-      </c>
-      <c r="M100" t="s">
-        <v>332</v>
-      </c>
-      <c r="N100" t="s">
-        <v>333</v>
-      </c>
-      <c r="O100" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="101" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L101" t="s">
-        <v>88</v>
-      </c>
-      <c r="M101" t="s">
-        <v>307</v>
-      </c>
-      <c r="N101" t="s">
-        <v>308</v>
-      </c>
-      <c r="O101" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="102" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L102" t="s">
-        <v>88</v>
-      </c>
-      <c r="M102" t="s">
-        <v>334</v>
-      </c>
-      <c r="N102" t="s">
-        <v>335</v>
-      </c>
-      <c r="O102" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="103" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L103" t="s">
-        <v>88</v>
-      </c>
-      <c r="M103" t="s">
-        <v>336</v>
-      </c>
-      <c r="N103" t="s">
-        <v>337</v>
-      </c>
-      <c r="O103" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="104" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L104" t="s">
-        <v>88</v>
-      </c>
-      <c r="M104" t="s">
-        <v>271</v>
-      </c>
-      <c r="N104" t="s">
-        <v>272</v>
-      </c>
-      <c r="O104" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="105" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L105" t="s">
-        <v>88</v>
-      </c>
-      <c r="M105" t="s">
-        <v>338</v>
-      </c>
-      <c r="N105" t="s">
-        <v>339</v>
-      </c>
-      <c r="O105" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="106" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L106" t="s">
-        <v>88</v>
-      </c>
-      <c r="M106" t="s">
-        <v>340</v>
-      </c>
-      <c r="N106" t="s">
-        <v>341</v>
-      </c>
-      <c r="O106" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="107" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L107" t="s">
-        <v>88</v>
-      </c>
-      <c r="M107" t="s">
-        <v>342</v>
-      </c>
-      <c r="N107" t="s">
-        <v>343</v>
-      </c>
-      <c r="O107" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="108" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L108" t="s">
-        <v>88</v>
-      </c>
-      <c r="M108" t="s">
-        <v>321</v>
-      </c>
-      <c r="N108" t="s">
-        <v>322</v>
-      </c>
-      <c r="O108" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="109" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L109" t="s">
-        <v>88</v>
-      </c>
-      <c r="M109" t="s">
-        <v>303</v>
-      </c>
-      <c r="N109" t="s">
-        <v>304</v>
-      </c>
-      <c r="O109" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="110" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L110" t="s">
-        <v>88</v>
-      </c>
-      <c r="M110" t="s">
-        <v>344</v>
-      </c>
-      <c r="N110" t="s">
-        <v>345</v>
-      </c>
-      <c r="O110" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="111" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L111" t="s">
-        <v>88</v>
-      </c>
-      <c r="M111" t="s">
-        <v>346</v>
-      </c>
-      <c r="N111" t="s">
-        <v>347</v>
-      </c>
-      <c r="O111" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="112" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L112" t="s">
-        <v>88</v>
-      </c>
-      <c r="M112" t="s">
-        <v>348</v>
-      </c>
-      <c r="N112" t="s">
-        <v>349</v>
-      </c>
-      <c r="O112" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="113" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L113" t="s">
-        <v>88</v>
-      </c>
-      <c r="M113" t="s">
-        <v>350</v>
-      </c>
-      <c r="N113" t="s">
-        <v>351</v>
-      </c>
-      <c r="O113" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="114" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L114" t="s">
-        <v>88</v>
-      </c>
-      <c r="M114" t="s">
-        <v>352</v>
-      </c>
-      <c r="N114" t="s">
-        <v>353</v>
-      </c>
-      <c r="O114" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="115" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L115" t="s">
-        <v>88</v>
-      </c>
-      <c r="M115" t="s">
-        <v>354</v>
-      </c>
-      <c r="N115" t="s">
-        <v>355</v>
-      </c>
-      <c r="O115" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="116" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L116" t="s">
-        <v>88</v>
-      </c>
-      <c r="M116" t="s">
-        <v>356</v>
-      </c>
-      <c r="N116" t="s">
-        <v>357</v>
-      </c>
-      <c r="O116" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="117" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L117" t="s">
-        <v>88</v>
-      </c>
-      <c r="M117" t="s">
-        <v>358</v>
-      </c>
-      <c r="N117" t="s">
-        <v>359</v>
-      </c>
-      <c r="O117" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="118" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L118" t="s">
-        <v>88</v>
-      </c>
-      <c r="M118" t="s">
-        <v>360</v>
-      </c>
-      <c r="N118" t="s">
-        <v>361</v>
-      </c>
-      <c r="O118" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="119" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L119" t="s">
-        <v>88</v>
-      </c>
-      <c r="M119" t="s">
-        <v>362</v>
-      </c>
-      <c r="N119" t="s">
-        <v>363</v>
-      </c>
-      <c r="O119" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="120" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L120" t="s">
-        <v>88</v>
-      </c>
-      <c r="M120" t="s">
-        <v>364</v>
-      </c>
-      <c r="N120" t="s">
-        <v>365</v>
-      </c>
-      <c r="O120" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="121" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L121" t="s">
-        <v>88</v>
-      </c>
-      <c r="M121" t="s">
-        <v>366</v>
-      </c>
-      <c r="N121" t="s">
-        <v>367</v>
-      </c>
-      <c r="O121" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="122" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L122" t="s">
-        <v>88</v>
-      </c>
-      <c r="M122" t="s">
-        <v>368</v>
-      </c>
-      <c r="N122" t="s">
-        <v>369</v>
-      </c>
-      <c r="O122" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="123" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L123" t="s">
-        <v>88</v>
-      </c>
-      <c r="M123" t="s">
-        <v>370</v>
-      </c>
-      <c r="N123" t="s">
-        <v>371</v>
-      </c>
-      <c r="O123" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="124" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L124" t="s">
-        <v>88</v>
-      </c>
-      <c r="M124" t="s">
-        <v>372</v>
-      </c>
-      <c r="N124" t="s">
-        <v>373</v>
-      </c>
-      <c r="O124" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="125" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L125" t="s">
-        <v>88</v>
-      </c>
-      <c r="M125" t="s">
-        <v>374</v>
-      </c>
-      <c r="N125" t="s">
-        <v>375</v>
-      </c>
-      <c r="O125" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="126" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L126" t="s">
-        <v>88</v>
-      </c>
-      <c r="M126" t="s">
-        <v>376</v>
-      </c>
-      <c r="N126" t="s">
-        <v>377</v>
-      </c>
-      <c r="O126" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="127" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L127" t="s">
-        <v>88</v>
-      </c>
-      <c r="M127" t="s">
-        <v>378</v>
-      </c>
-      <c r="N127" t="s">
-        <v>379</v>
-      </c>
-      <c r="O127" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="128" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L128" t="s">
-        <v>88</v>
-      </c>
-      <c r="M128" t="s">
-        <v>257</v>
-      </c>
-      <c r="N128" t="s">
-        <v>258</v>
-      </c>
-      <c r="O128" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="129" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L129" t="s">
-        <v>88</v>
-      </c>
-      <c r="M129" t="s">
-        <v>380</v>
-      </c>
-      <c r="N129" t="s">
-        <v>381</v>
-      </c>
-      <c r="O129" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="130" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L130" t="s">
-        <v>88</v>
-      </c>
-      <c r="M130" t="s">
-        <v>382</v>
-      </c>
-      <c r="N130" t="s">
-        <v>383</v>
-      </c>
-      <c r="O130" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="131" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L131" t="s">
-        <v>88</v>
-      </c>
-      <c r="M131" t="s">
-        <v>384</v>
-      </c>
-      <c r="N131" t="s">
-        <v>385</v>
-      </c>
-      <c r="O131" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="132" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L132" t="s">
-        <v>88</v>
-      </c>
-      <c r="M132" t="s">
-        <v>386</v>
-      </c>
-      <c r="N132" t="s">
+      <c r="J158" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="159" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G159" t="s">
+        <v>88</v>
+      </c>
+      <c r="H159" t="s">
         <v>387</v>
       </c>
-      <c r="O132" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="133" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L133" t="s">
-        <v>88</v>
-      </c>
-      <c r="M133" t="s">
+      <c r="I159" t="s">
         <v>388</v>
       </c>
-      <c r="N133" t="s">
+      <c r="J159" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="160" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G160" t="s">
+        <v>88</v>
+      </c>
+      <c r="H160" t="s">
         <v>389</v>
       </c>
-      <c r="O133" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="134" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L134" t="s">
-        <v>88</v>
-      </c>
-      <c r="M134" t="s">
-        <v>259</v>
-      </c>
-      <c r="N134" t="s">
-        <v>260</v>
-      </c>
-      <c r="O134" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="135" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L135" t="s">
-        <v>88</v>
-      </c>
-      <c r="M135" t="s">
-        <v>261</v>
-      </c>
-      <c r="N135" t="s">
-        <v>262</v>
-      </c>
-      <c r="O135" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="136" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L136" t="s">
-        <v>88</v>
-      </c>
-      <c r="M136" t="s">
-        <v>263</v>
-      </c>
-      <c r="N136" t="s">
-        <v>264</v>
-      </c>
-      <c r="O136" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="137" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L137" t="s">
-        <v>88</v>
-      </c>
-      <c r="M137" t="s">
-        <v>265</v>
-      </c>
-      <c r="N137" t="s">
-        <v>266</v>
-      </c>
-      <c r="O137" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="138" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L138" t="s">
-        <v>88</v>
-      </c>
-      <c r="M138" t="s">
-        <v>267</v>
-      </c>
-      <c r="N138" t="s">
-        <v>268</v>
-      </c>
-      <c r="O138" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="139" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L139" t="s">
-        <v>88</v>
-      </c>
-      <c r="M139" t="s">
-        <v>269</v>
-      </c>
-      <c r="N139" t="s">
-        <v>270</v>
-      </c>
-      <c r="O139" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="140" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L140" t="s">
-        <v>88</v>
-      </c>
-      <c r="M140" t="s">
-        <v>273</v>
-      </c>
-      <c r="N140" t="s">
-        <v>274</v>
-      </c>
-      <c r="O140" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="141" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L141" t="s">
-        <v>88</v>
-      </c>
-      <c r="M141" t="s">
-        <v>275</v>
-      </c>
-      <c r="N141" t="s">
-        <v>276</v>
-      </c>
-      <c r="O141" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="142" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L142" t="s">
-        <v>88</v>
-      </c>
-      <c r="M142" t="s">
-        <v>277</v>
-      </c>
-      <c r="N142" t="s">
-        <v>278</v>
-      </c>
-      <c r="O142" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="143" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L143" t="s">
-        <v>88</v>
-      </c>
-      <c r="M143" t="s">
-        <v>279</v>
-      </c>
-      <c r="N143" t="s">
-        <v>280</v>
-      </c>
-      <c r="O143" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="144" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L144" t="s">
-        <v>88</v>
-      </c>
-      <c r="M144" t="s">
-        <v>281</v>
-      </c>
-      <c r="N144" t="s">
-        <v>282</v>
-      </c>
-      <c r="O144" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="145" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L145" t="s">
-        <v>88</v>
-      </c>
-      <c r="M145" t="s">
-        <v>283</v>
-      </c>
-      <c r="N145" t="s">
-        <v>284</v>
-      </c>
-      <c r="O145" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="146" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L146" t="s">
-        <v>88</v>
-      </c>
-      <c r="M146" t="s">
-        <v>285</v>
-      </c>
-      <c r="N146" t="s">
-        <v>286</v>
-      </c>
-      <c r="O146" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="147" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L147" t="s">
-        <v>88</v>
-      </c>
-      <c r="M147" t="s">
-        <v>287</v>
-      </c>
-      <c r="N147" t="s">
-        <v>288</v>
-      </c>
-      <c r="O147" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="148" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L148" t="s">
-        <v>88</v>
-      </c>
-      <c r="M148" t="s">
-        <v>289</v>
-      </c>
-      <c r="N148" t="s">
-        <v>290</v>
-      </c>
-      <c r="O148" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="149" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L149" t="s">
-        <v>88</v>
-      </c>
-      <c r="M149" t="s">
-        <v>293</v>
-      </c>
-      <c r="N149" t="s">
-        <v>294</v>
-      </c>
-      <c r="O149" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="150" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L150" t="s">
-        <v>88</v>
-      </c>
-      <c r="M150" t="s">
-        <v>297</v>
-      </c>
-      <c r="N150" t="s">
-        <v>298</v>
-      </c>
-      <c r="O150" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="151" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L151" t="s">
-        <v>88</v>
-      </c>
-      <c r="M151" t="s">
-        <v>301</v>
-      </c>
-      <c r="N151" t="s">
-        <v>302</v>
-      </c>
-      <c r="O151" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="152" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L152" t="s">
-        <v>88</v>
-      </c>
-      <c r="M152" t="s">
-        <v>305</v>
-      </c>
-      <c r="N152" t="s">
-        <v>306</v>
-      </c>
-      <c r="O152" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="153" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L153" t="s">
-        <v>88</v>
-      </c>
-      <c r="M153" t="s">
-        <v>309</v>
-      </c>
-      <c r="N153" t="s">
-        <v>310</v>
-      </c>
-      <c r="O153" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="154" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L154" t="s">
-        <v>88</v>
-      </c>
-      <c r="M154" t="s">
-        <v>311</v>
-      </c>
-      <c r="N154" t="s">
-        <v>312</v>
-      </c>
-      <c r="O154" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="155" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L155" t="s">
-        <v>88</v>
-      </c>
-      <c r="M155" t="s">
-        <v>313</v>
-      </c>
-      <c r="N155" t="s">
-        <v>314</v>
-      </c>
-      <c r="O155" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="156" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L156" t="s">
-        <v>88</v>
-      </c>
-      <c r="M156" t="s">
-        <v>315</v>
-      </c>
-      <c r="N156" t="s">
-        <v>316</v>
-      </c>
-      <c r="O156" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="157" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L157" t="s">
-        <v>88</v>
-      </c>
-      <c r="M157" t="s">
-        <v>317</v>
-      </c>
-      <c r="N157" t="s">
-        <v>318</v>
-      </c>
-      <c r="O157" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="158" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L158" t="s">
-        <v>88</v>
-      </c>
-      <c r="M158" t="s">
-        <v>319</v>
-      </c>
-      <c r="N158" t="s">
-        <v>320</v>
-      </c>
-      <c r="O158" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="159" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L159" t="s">
-        <v>88</v>
-      </c>
-      <c r="M159" t="s">
-        <v>323</v>
-      </c>
-      <c r="N159" t="s">
-        <v>324</v>
-      </c>
-      <c r="O159" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="160" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L160" t="s">
-        <v>88</v>
-      </c>
-      <c r="M160" t="s">
+      <c r="I160" t="s">
         <v>390</v>
       </c>
-      <c r="N160" t="s">
+      <c r="J160" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="161" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G161" t="s">
+        <v>88</v>
+      </c>
+      <c r="H161" t="s">
         <v>391</v>
       </c>
-      <c r="O160" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="161" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L161" t="s">
-        <v>88</v>
-      </c>
-      <c r="M161" t="s">
+      <c r="I161" t="s">
         <v>392</v>
       </c>
-      <c r="N161" t="s">
+      <c r="J161" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="162" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G162" t="s">
+        <v>88</v>
+      </c>
+      <c r="H162" t="s">
         <v>393</v>
       </c>
-      <c r="O161" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="162" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L162" t="s">
-        <v>88</v>
-      </c>
-      <c r="M162" t="s">
+      <c r="I162" t="s">
         <v>394</v>
       </c>
-      <c r="N162" t="s">
+      <c r="J162" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="163" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G163" t="s">
+        <v>88</v>
+      </c>
+      <c r="H163" t="s">
         <v>395</v>
       </c>
-      <c r="O162" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="163" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L163" t="s">
-        <v>88</v>
-      </c>
-      <c r="M163" t="s">
+      <c r="I163" t="s">
         <v>396</v>
       </c>
-      <c r="N163" t="s">
+      <c r="J163" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="164" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G164" t="s">
+        <v>88</v>
+      </c>
+      <c r="H164" t="s">
         <v>397</v>
       </c>
-      <c r="O163" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="164" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L164" t="s">
-        <v>88</v>
-      </c>
-      <c r="M164" t="s">
+      <c r="I164" t="s">
         <v>398</v>
       </c>
-      <c r="N164" t="s">
+      <c r="J164" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="165" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G165" t="s">
+        <v>88</v>
+      </c>
+      <c r="H165" t="s">
         <v>399</v>
       </c>
-      <c r="O164" t="s">
-        <v>325</v>
+      <c r="I165" t="s">
+        <v>400</v>
+      </c>
+      <c r="J165" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="166" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G166" t="s">
+        <v>88</v>
+      </c>
+      <c r="H166" t="s">
+        <v>401</v>
+      </c>
+      <c r="I166" t="s">
+        <v>402</v>
+      </c>
+      <c r="J166" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
